--- a/experiment/SwinT2+CNN_2CH_bestx4/Collect/SwinT_Collect.xlsx
+++ b/experiment/SwinT2+CNN_2CH_bestx4/Collect/SwinT_Collect.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gama\Desktop\New folder\SwinT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohamed\Desktop\New folder\SwinT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EAE4603-B91F-4AE8-A490-9F1193867E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF56D2A-9722-496B-B13C-B39E759B2384}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PSNR" sheetId="1" r:id="rId1"/>
@@ -53,14 +53,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="4">
@@ -112,14 +112,14 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -397,59 +397,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F407"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F411"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2">
         <v>28.780999999999999</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>29.221</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>28.042999999999999</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>29.048999999999999</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>29.099</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>29.039000000000001</v>
       </c>
       <c r="C3">
@@ -458,74 +458,74 @@
       <c r="D3">
         <v>27.920999999999999</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>29.337</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="1">
         <v>29.388000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>29.233000000000001</v>
       </c>
       <c r="C4">
         <v>28.858000000000001</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>29.585999999999999</v>
       </c>
       <c r="E4">
         <v>28.635000000000002</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>29.440999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>28.885000000000002</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>30.245000000000001</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>30.052</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>30.068999999999999</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>30.181999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6">
         <v>29.221</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>30.611000000000001</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>30.425999999999998</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>30.672999999999998</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="1">
         <v>30.382000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5</v>
       </c>
@@ -535,27 +535,27 @@
       <c r="C7">
         <v>30.326000000000001</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <v>30.673999999999999</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>30.808</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="1">
         <v>30.777000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>29.908000000000001</v>
       </c>
       <c r="C8">
         <v>30.381</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>30.733000000000001</v>
       </c>
       <c r="E8">
@@ -565,34 +565,34 @@
         <v>30.222000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>30.199000000000002</v>
       </c>
       <c r="C9">
         <v>30.302</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>30.824999999999999</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>31.01</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="1">
         <v>30.920999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>30.399000000000001</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <v>31.148</v>
       </c>
       <c r="D10">
@@ -601,15 +601,15 @@
       <c r="E10">
         <v>30.911999999999999</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="1">
         <v>30.975999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>30.567</v>
       </c>
       <c r="C11">
@@ -618,101 +618,101 @@
       <c r="D11">
         <v>30.783999999999999</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>31.085000000000001</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="1">
         <v>31.109000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <v>30.719000000000001</v>
       </c>
       <c r="C12">
         <v>30.28</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>30.872</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>31.093</v>
       </c>
       <c r="F12">
         <v>31.076000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>30.838000000000001</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="1">
         <v>31.298999999999999</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>31.027999999999999</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>31.238</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <v>31.111999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>30.957000000000001</v>
       </c>
       <c r="C14">
         <v>30.841999999999999</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>31.164999999999999</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>31.327000000000002</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="1">
         <v>31.286000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <v>31.067</v>
       </c>
       <c r="C15">
         <v>31.175999999999998</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>31.231999999999999</v>
       </c>
       <c r="E15">
         <v>30.672999999999998</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="1">
         <v>31.344000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>31.1</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="1">
         <v>31.35</v>
       </c>
       <c r="D16">
@@ -725,34 +725,34 @@
         <v>31.27</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>31.177</v>
       </c>
       <c r="C17">
         <v>31.315999999999999</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="1">
         <v>31.280999999999999</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="1">
         <v>31.38</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="1">
         <v>31.361000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="1">
         <v>31.231999999999999</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="1">
         <v>31.376000000000001</v>
       </c>
       <c r="D18">
@@ -765,11 +765,11 @@
         <v>31.338999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="1">
         <v>30.983000000000001</v>
       </c>
       <c r="C19">
@@ -781,11 +781,11 @@
       <c r="E19">
         <v>31.277999999999999</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="1">
         <v>31.396000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>18</v>
       </c>
@@ -795,57 +795,57 @@
       <c r="C20">
         <v>31.373000000000001</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="1">
         <v>31.405999999999999</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="1">
         <v>31.54</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="1">
         <v>31.405000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="1">
         <v>31.324999999999999</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="1">
         <v>31.407</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="1">
         <v>31.411999999999999</v>
       </c>
       <c r="E21">
         <v>31.431000000000001</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="1">
         <v>31.541</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="1">
         <v>30.617999999999999</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="1">
         <v>31.474</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="1">
         <v>31.436</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="1">
         <v>31.553000000000001</v>
       </c>
       <c r="F22">
         <v>31.11</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>21</v>
       </c>
@@ -855,7 +855,7 @@
       <c r="C23">
         <v>31.437999999999999</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="1">
         <v>31.5</v>
       </c>
       <c r="E23">
@@ -865,7 +865,7 @@
         <v>31.053000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>22</v>
       </c>
@@ -878,38 +878,38 @@
       <c r="D24">
         <v>31.459</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="1">
         <v>31.553000000000001</v>
       </c>
       <c r="F24">
         <v>31.518999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>23</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="1">
         <v>31.501999999999999</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="1">
         <v>31.532</v>
       </c>
       <c r="D25">
         <v>31.321999999999999</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="1">
         <v>31.6</v>
       </c>
       <c r="F25">
         <v>31.416</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>24</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="1">
         <v>31.574000000000002</v>
       </c>
       <c r="C26">
@@ -918,24 +918,24 @@
       <c r="D26">
         <v>31.465</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="1">
         <v>31.640999999999998</v>
       </c>
       <c r="F26">
         <v>31.433</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>25</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="1">
         <v>31.399000000000001</v>
       </c>
       <c r="C27">
         <v>31.018000000000001</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="1">
         <v>31.513000000000002</v>
       </c>
       <c r="E27">
@@ -945,7 +945,7 @@
         <v>31.364000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>26</v>
       </c>
@@ -961,21 +961,21 @@
       <c r="E28">
         <v>31.571000000000002</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="1">
         <v>31.550999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29">
         <v>31.565000000000001</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="1">
         <v>31.632000000000001</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="1">
         <v>31.562000000000001</v>
       </c>
       <c r="E29">
@@ -985,7 +985,7 @@
         <v>31.491</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>31.376999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1025,11 +1025,11 @@
         <v>31.45</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>30</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="1">
         <v>31.780999999999999</v>
       </c>
       <c r="C32">
@@ -1038,18 +1038,18 @@
       <c r="D32">
         <v>31.47</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" s="1">
         <v>31.681999999999999</v>
       </c>
       <c r="F32">
         <v>31.506</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>31</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="1">
         <v>31.795000000000002</v>
       </c>
       <c r="C33">
@@ -1065,27 +1065,27 @@
         <v>31.513000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>32</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="1">
         <v>31.783000000000001</v>
       </c>
       <c r="C34">
         <v>31.443999999999999</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="1">
         <v>31.611999999999998</v>
       </c>
       <c r="E34">
         <v>31.597000000000001</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="1">
         <v>31.588999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1095,57 +1095,57 @@
       <c r="C35">
         <v>31.611000000000001</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="1">
         <v>31.625</v>
       </c>
       <c r="E35">
         <v>31.564</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="1">
         <v>31.600999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>34</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="1">
         <v>31.849</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="1">
         <v>31.774000000000001</v>
       </c>
       <c r="D36">
         <v>31.603999999999999</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="1">
         <v>31.704000000000001</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="1">
         <v>31.640999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>35</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="1">
         <v>31.483000000000001</v>
       </c>
       <c r="C37">
         <v>31.655999999999999</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="1">
         <v>31.7</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="1">
         <v>31.715</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="1">
         <v>31.681999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1165,7 +1165,7 @@
         <v>31.657</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1185,7 +1185,7 @@
         <v>31.21</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1198,18 +1198,18 @@
       <c r="D40">
         <v>31.696999999999999</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E40" s="1">
         <v>31.736000000000001</v>
       </c>
       <c r="F40">
         <v>31.542000000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>39</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="1">
         <v>31.632999999999999</v>
       </c>
       <c r="C41">
@@ -1218,14 +1218,14 @@
       <c r="D41">
         <v>31.577999999999999</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E41" s="1">
         <v>31.768000000000001</v>
       </c>
       <c r="F41">
         <v>31.651</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1238,38 +1238,38 @@
       <c r="D42">
         <v>31.677</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="1">
         <v>31.78</v>
       </c>
       <c r="F42">
         <v>31.344999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>41</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="1">
         <v>31.946000000000002</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="1">
         <v>31.821999999999999</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="1">
         <v>31.722000000000001</v>
       </c>
       <c r="E43">
         <v>31.748000000000001</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="1">
         <v>31.718</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>42</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="1">
         <v>31.776</v>
       </c>
       <c r="C44">
@@ -1285,7 +1285,7 @@
         <v>31.640999999999998</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1295,7 +1295,7 @@
       <c r="C45">
         <v>31.663</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="1">
         <v>31.742000000000001</v>
       </c>
       <c r="E45">
@@ -1305,7 +1305,7 @@
         <v>31.672999999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1325,27 +1325,27 @@
         <v>31.62</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>45</v>
       </c>
       <c r="B47">
         <v>31.94</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="1">
         <v>31.824000000000002</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="1">
         <v>31.751999999999999</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E47" s="1">
         <v>31.791</v>
       </c>
       <c r="F47">
         <v>31.67</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>46</v>
       </c>
@@ -1355,21 +1355,21 @@
       <c r="C48">
         <v>31.777999999999999</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="1">
         <v>31.78</v>
       </c>
       <c r="E48">
         <v>31.722999999999999</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="1">
         <v>31.745000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>47</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="1">
         <v>31.881</v>
       </c>
       <c r="C49">
@@ -1385,7 +1385,7 @@
         <v>31.727</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>48</v>
       </c>
@@ -1395,27 +1395,27 @@
       <c r="C50">
         <v>31.655999999999999</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="1">
         <v>31.795000000000002</v>
       </c>
       <c r="E50">
         <v>31.696999999999999</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="1">
         <v>31.832000000000001</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>49</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="1">
         <v>31.981999999999999</v>
       </c>
       <c r="C51">
         <v>31.187999999999999</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="1">
         <v>31.817</v>
       </c>
       <c r="E51">
@@ -1425,34 +1425,34 @@
         <v>31.802</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>50</v>
       </c>
       <c r="B52">
         <v>32.008000000000003</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" s="1">
         <v>31.826000000000001</v>
       </c>
       <c r="D52">
         <v>31.791</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E52" s="1">
         <v>31.834</v>
       </c>
       <c r="F52">
         <v>31.745000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>51</v>
       </c>
       <c r="B53">
         <v>31.99</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="1">
         <v>31.838000000000001</v>
       </c>
       <c r="D53">
@@ -1461,11 +1461,11 @@
       <c r="E53">
         <v>31.818999999999999</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="1">
         <v>31.893999999999998</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>52</v>
       </c>
@@ -1478,38 +1478,38 @@
       <c r="D54">
         <v>31.574999999999999</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E54" s="1">
         <v>31.85</v>
       </c>
       <c r="F54">
         <v>31.699000000000002</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>53</v>
       </c>
       <c r="B55">
         <v>32.075000000000003</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="1">
         <v>31.838999999999999</v>
       </c>
-      <c r="D55" s="2">
+      <c r="D55" s="1">
         <v>31.856999999999999</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E55" s="1">
         <v>31.923999999999999</v>
       </c>
       <c r="F55">
         <v>31.754999999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>54</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="1">
         <v>32.098999999999997</v>
       </c>
       <c r="C56">
@@ -1525,11 +1525,11 @@
         <v>31.75</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>55</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="1">
         <v>31.969000000000001</v>
       </c>
       <c r="C57">
@@ -1545,14 +1545,14 @@
         <v>31.766999999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>56</v>
       </c>
       <c r="B58">
         <v>31.919</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58" s="1">
         <v>31.885000000000002</v>
       </c>
       <c r="D58">
@@ -1565,7 +1565,7 @@
         <v>31.812999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>57</v>
       </c>
@@ -1575,21 +1575,21 @@
       <c r="C59">
         <v>31.759</v>
       </c>
-      <c r="D59" s="2">
+      <c r="D59" s="1">
         <v>31.876000000000001</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E59" s="1">
         <v>31.962</v>
       </c>
       <c r="F59">
         <v>31.834</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>58</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="1">
         <v>32.136000000000003</v>
       </c>
       <c r="C60">
@@ -1605,11 +1605,11 @@
         <v>31.849</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>59</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="1">
         <v>31.99</v>
       </c>
       <c r="C61">
@@ -1625,7 +1625,7 @@
         <v>31.843</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>60</v>
       </c>
@@ -1645,34 +1645,34 @@
         <v>31.852</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>61</v>
       </c>
       <c r="B63">
         <v>32.158999999999999</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C63" s="1">
         <v>31.928000000000001</v>
       </c>
-      <c r="D63" s="2">
+      <c r="D63" s="1">
         <v>31.876999999999999</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E63" s="1">
         <v>31.965</v>
       </c>
       <c r="F63">
         <v>31.893000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>62</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64" s="1">
         <v>32.134</v>
       </c>
-      <c r="C64" s="2">
+      <c r="C64" s="1">
         <v>31.943000000000001</v>
       </c>
       <c r="D64">
@@ -1681,11 +1681,11 @@
       <c r="E64">
         <v>31.837</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="1">
         <v>31.925999999999998</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>63</v>
       </c>
@@ -1695,7 +1695,7 @@
       <c r="C65">
         <v>31.806000000000001</v>
       </c>
-      <c r="D65" s="2">
+      <c r="D65" s="1">
         <v>31.89</v>
       </c>
       <c r="E65">
@@ -1705,7 +1705,7 @@
         <v>31.79</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>64</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>31.875</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>65</v>
       </c>
@@ -1735,7 +1735,7 @@
       <c r="C67">
         <v>31.899000000000001</v>
       </c>
-      <c r="D67" s="2">
+      <c r="D67" s="1">
         <v>31.960999999999999</v>
       </c>
       <c r="E67">
@@ -1745,14 +1745,14 @@
         <v>31.640999999999998</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>66</v>
       </c>
       <c r="B68">
         <v>32.204000000000001</v>
       </c>
-      <c r="C68" s="2">
+      <c r="C68" s="1">
         <v>31.969000000000001</v>
       </c>
       <c r="D68">
@@ -1765,11 +1765,11 @@
         <v>31.861999999999998</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>67</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="1">
         <v>32.177</v>
       </c>
       <c r="C69">
@@ -1778,14 +1778,14 @@
       <c r="D69">
         <v>31.919</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E69" s="1">
         <v>31.97</v>
       </c>
       <c r="F69">
         <v>31.783999999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>68</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>31.827000000000002</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>69</v>
       </c>
@@ -1825,7 +1825,7 @@
         <v>31.878</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>70</v>
       </c>
@@ -1838,14 +1838,14 @@
       <c r="D72">
         <v>31.934000000000001</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E72" s="1">
         <v>31.971</v>
       </c>
       <c r="F72">
         <v>31.867000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>71</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>31.779</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>72</v>
       </c>
@@ -1881,15 +1881,15 @@
       <c r="E74">
         <v>31.946999999999999</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="1">
         <v>31.946999999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>73</v>
       </c>
-      <c r="B75" s="2">
+      <c r="B75" s="1">
         <v>32.131</v>
       </c>
       <c r="C75">
@@ -1905,14 +1905,14 @@
         <v>31.852</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>74</v>
       </c>
       <c r="B76">
         <v>32.24</v>
       </c>
-      <c r="C76" s="2">
+      <c r="C76" s="1">
         <v>31.977</v>
       </c>
       <c r="D76">
@@ -1921,41 +1921,41 @@
       <c r="E76">
         <v>31.914999999999999</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="1">
         <v>31.984999999999999</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>75</v>
       </c>
-      <c r="B77" s="2">
+      <c r="B77" s="1">
         <v>32.264000000000003</v>
       </c>
       <c r="C77">
         <v>31.827999999999999</v>
       </c>
-      <c r="D77" s="2">
+      <c r="D77" s="1">
         <v>31.989000000000001</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E77" s="1">
         <v>31.975999999999999</v>
       </c>
       <c r="F77">
         <v>31.9</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>76</v>
       </c>
-      <c r="B78" s="2">
+      <c r="B78" s="1">
         <v>32.073999999999998</v>
       </c>
       <c r="C78">
         <v>31.972999999999999</v>
       </c>
-      <c r="D78" s="2">
+      <c r="D78" s="1">
         <v>32.006999999999998</v>
       </c>
       <c r="E78">
@@ -1965,7 +1965,7 @@
         <v>31.951000000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>77</v>
       </c>
@@ -1975,17 +1975,17 @@
       <c r="C79">
         <v>31.861999999999998</v>
       </c>
-      <c r="D79" s="2">
+      <c r="D79" s="1">
         <v>32.011000000000003</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E79" s="1">
         <v>31.998000000000001</v>
       </c>
       <c r="F79">
         <v>31.963000000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>78</v>
       </c>
@@ -1998,14 +1998,14 @@
       <c r="D80">
         <v>31.934999999999999</v>
       </c>
-      <c r="E80" s="2">
+      <c r="E80" s="1">
         <v>31.998999999999999</v>
       </c>
       <c r="F80">
         <v>31.89</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>79</v>
       </c>
@@ -2018,14 +2018,14 @@
       <c r="D81">
         <v>32.006</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E81" s="1">
         <v>32.012999999999998</v>
       </c>
       <c r="F81">
         <v>31.861999999999998</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>80</v>
       </c>
@@ -2045,34 +2045,34 @@
         <v>31.934999999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>81</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="1">
         <v>32.316000000000003</v>
       </c>
       <c r="C83">
         <v>31.689</v>
       </c>
-      <c r="D83" s="2">
+      <c r="D83" s="1">
         <v>32.012999999999998</v>
       </c>
-      <c r="E83" s="2">
+      <c r="E83" s="1">
         <v>32.091999999999999</v>
       </c>
       <c r="F83">
         <v>31.943999999999999</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>82</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84" s="1">
         <v>32.283000000000001</v>
       </c>
-      <c r="C84" s="2">
+      <c r="C84" s="1">
         <v>32.018999999999998</v>
       </c>
       <c r="D84">
@@ -2085,7 +2085,7 @@
         <v>31.890999999999998</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>83</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>31.861999999999998</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>84</v>
       </c>
@@ -2115,7 +2115,7 @@
       <c r="C86">
         <v>31.942</v>
       </c>
-      <c r="D86" s="2">
+      <c r="D86" s="1">
         <v>32.021000000000001</v>
       </c>
       <c r="E86">
@@ -2125,7 +2125,7 @@
         <v>31.869</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>85</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>31.79</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>86</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>31.981999999999999</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>87</v>
       </c>
@@ -2185,14 +2185,14 @@
         <v>31.952000000000002</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>88</v>
       </c>
       <c r="B90">
         <v>32.337000000000003</v>
       </c>
-      <c r="C90" s="2">
+      <c r="C90" s="1">
         <v>32.024999999999999</v>
       </c>
       <c r="D90">
@@ -2201,15 +2201,15 @@
       <c r="E90">
         <v>32.046999999999997</v>
       </c>
-      <c r="F90" s="2">
+      <c r="F90" s="1">
         <v>31.995000000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>89</v>
       </c>
-      <c r="B91" s="2">
+      <c r="B91" s="1">
         <v>32.250999999999998</v>
       </c>
       <c r="C91">
@@ -2225,14 +2225,14 @@
         <v>31.977</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>90</v>
       </c>
       <c r="B92">
         <v>32.307000000000002</v>
       </c>
-      <c r="C92" s="2">
+      <c r="C92" s="1">
         <v>32.036000000000001</v>
       </c>
       <c r="D92">
@@ -2241,11 +2241,11 @@
       <c r="E92">
         <v>32.006999999999998</v>
       </c>
-      <c r="F92" s="2">
+      <c r="F92" s="1">
         <v>32.012</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>91</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>31.913</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>92</v>
       </c>
@@ -2285,11 +2285,11 @@
         <v>31.859000000000002</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>93</v>
       </c>
-      <c r="B95" s="2">
+      <c r="B95" s="1">
         <v>32.332000000000001</v>
       </c>
       <c r="C95">
@@ -2301,11 +2301,11 @@
       <c r="E95">
         <v>32.042999999999999</v>
       </c>
-      <c r="F95" s="2">
+      <c r="F95" s="1">
         <v>32.026000000000003</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>94</v>
       </c>
@@ -2321,21 +2321,21 @@
       <c r="E96">
         <v>32.072000000000003</v>
       </c>
-      <c r="F96" s="2">
+      <c r="F96" s="1">
         <v>32.034999999999997</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>95</v>
       </c>
       <c r="B97">
         <v>32.359000000000002</v>
       </c>
-      <c r="C97" s="2">
+      <c r="C97" s="1">
         <v>32.040999999999997</v>
       </c>
-      <c r="D97" s="2">
+      <c r="D97" s="1">
         <v>32.027000000000001</v>
       </c>
       <c r="E97">
@@ -2345,14 +2345,14 @@
         <v>31.997</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>96</v>
       </c>
       <c r="B98">
         <v>32.204999999999998</v>
       </c>
-      <c r="C98" s="2">
+      <c r="C98" s="1">
         <v>32.042000000000002</v>
       </c>
       <c r="D98">
@@ -2361,11 +2361,11 @@
       <c r="E98">
         <v>32.042000000000002</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="1">
         <v>32.046999999999997</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>97</v>
       </c>
@@ -2375,7 +2375,7 @@
       <c r="C99">
         <v>31.952000000000002</v>
       </c>
-      <c r="D99" s="2">
+      <c r="D99" s="1">
         <v>32.06</v>
       </c>
       <c r="E99">
@@ -2385,7 +2385,7 @@
         <v>31.995999999999999</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>98</v>
       </c>
@@ -2405,11 +2405,11 @@
         <v>31.992000000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>99</v>
       </c>
-      <c r="B101" s="2">
+      <c r="B101" s="1">
         <v>32.381999999999998</v>
       </c>
       <c r="C101">
@@ -2425,7 +2425,7 @@
         <v>32.012999999999998</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>100</v>
       </c>
@@ -2435,17 +2435,17 @@
       <c r="C102">
         <v>32.033000000000001</v>
       </c>
-      <c r="D102" s="2">
+      <c r="D102" s="1">
         <v>32.061</v>
       </c>
       <c r="E102">
         <v>32.057000000000002</v>
       </c>
-      <c r="F102" s="2">
+      <c r="F102" s="1">
         <v>32.048000000000002</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>101</v>
       </c>
@@ -2455,7 +2455,7 @@
       <c r="C103">
         <v>32.040999999999997</v>
       </c>
-      <c r="D103" s="2">
+      <c r="D103" s="1">
         <v>32.067999999999998</v>
       </c>
       <c r="E103">
@@ -2465,14 +2465,14 @@
         <v>32.026000000000003</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>102</v>
       </c>
       <c r="B104">
         <v>32.259</v>
       </c>
-      <c r="C104" s="2">
+      <c r="C104" s="1">
         <v>32.066000000000003</v>
       </c>
       <c r="D104">
@@ -2485,7 +2485,7 @@
         <v>32.040999999999997</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>103</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>32.03</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>104</v>
       </c>
@@ -2518,21 +2518,21 @@
       <c r="D106">
         <v>32.067</v>
       </c>
-      <c r="E106" s="2">
+      <c r="E106" s="1">
         <v>32.118000000000002</v>
       </c>
-      <c r="F106" s="2">
+      <c r="F106" s="1">
         <v>32.052999999999997</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>105</v>
       </c>
       <c r="B107">
         <v>32.4</v>
       </c>
-      <c r="C107" s="2">
+      <c r="C107" s="1">
         <v>32.084000000000003</v>
       </c>
       <c r="D107">
@@ -2545,14 +2545,14 @@
         <v>31.949000000000002</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>106</v>
       </c>
       <c r="B108">
         <v>32.329000000000001</v>
       </c>
-      <c r="C108" s="2">
+      <c r="C108" s="1">
         <v>32.103999999999999</v>
       </c>
       <c r="D108">
@@ -2565,7 +2565,7 @@
         <v>32.029000000000003</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>107</v>
       </c>
@@ -2575,17 +2575,17 @@
       <c r="C109">
         <v>32.067999999999998</v>
       </c>
-      <c r="D109" s="2">
+      <c r="D109" s="1">
         <v>32.122999999999998</v>
       </c>
       <c r="E109">
         <v>32.113</v>
       </c>
-      <c r="F109" s="2">
+      <c r="F109" s="1">
         <v>32.061999999999998</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>108</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>31.954000000000001</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>109</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>31.943999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>110</v>
       </c>
@@ -2638,18 +2638,18 @@
       <c r="D112">
         <v>32.064999999999998</v>
       </c>
-      <c r="E112" s="2">
+      <c r="E112" s="1">
         <v>32.121000000000002</v>
       </c>
       <c r="F112">
         <v>32.058</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>111</v>
       </c>
-      <c r="B113" s="2">
+      <c r="B113" s="1">
         <v>32.384999999999998</v>
       </c>
       <c r="C113">
@@ -2665,7 +2665,7 @@
         <v>31.984000000000002</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>112</v>
       </c>
@@ -2685,7 +2685,7 @@
         <v>32.005000000000003</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>113</v>
       </c>
@@ -2695,7 +2695,7 @@
       <c r="C115">
         <v>31.992999999999999</v>
       </c>
-      <c r="D115" s="2">
+      <c r="D115" s="1">
         <v>32.152999999999999</v>
       </c>
       <c r="E115">
@@ -2705,7 +2705,7 @@
         <v>31.968</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>114</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>32.002000000000002</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>115</v>
       </c>
@@ -2738,14 +2738,14 @@
       <c r="D117">
         <v>32.093000000000004</v>
       </c>
-      <c r="E117" s="2">
+      <c r="E117" s="1">
         <v>32.136000000000003</v>
       </c>
       <c r="F117">
         <v>32.058</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>116</v>
       </c>
@@ -2765,7 +2765,7 @@
         <v>32.049999999999997</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>117</v>
       </c>
@@ -2785,14 +2785,14 @@
         <v>32.058999999999997</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>118</v>
       </c>
       <c r="B120">
         <v>32.353999999999999</v>
       </c>
-      <c r="C120" s="2">
+      <c r="C120" s="1">
         <v>32.118000000000002</v>
       </c>
       <c r="D120">
@@ -2801,11 +2801,11 @@
       <c r="E120">
         <v>32.104999999999997</v>
       </c>
-      <c r="F120" s="2">
+      <c r="F120" s="1">
         <v>32.091000000000001</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>119</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>32.06</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>120</v>
       </c>
@@ -2845,17 +2845,17 @@
         <v>32.090000000000003</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>121</v>
       </c>
-      <c r="B123" s="2">
+      <c r="B123" s="1">
         <v>32.466999999999999</v>
       </c>
       <c r="C123">
         <v>32.042000000000002</v>
       </c>
-      <c r="D123" s="2">
+      <c r="D123" s="1">
         <v>32.17</v>
       </c>
       <c r="E123">
@@ -2865,7 +2865,7 @@
         <v>32.082999999999998</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>122</v>
       </c>
@@ -2885,27 +2885,27 @@
         <v>31.998999999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>123</v>
       </c>
-      <c r="B125" s="2">
+      <c r="B125" s="1">
         <v>32.319000000000003</v>
       </c>
-      <c r="C125" s="2">
+      <c r="C125" s="1">
         <v>32.122999999999998</v>
       </c>
       <c r="D125">
         <v>32.122</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E125" s="1">
         <v>32.177999999999997</v>
       </c>
       <c r="F125">
         <v>32.085999999999999</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>124</v>
       </c>
@@ -2925,14 +2925,14 @@
         <v>32.045000000000002</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>125</v>
       </c>
       <c r="B127">
         <v>32.4</v>
       </c>
-      <c r="C127" s="2">
+      <c r="C127" s="1">
         <v>32.143999999999998</v>
       </c>
       <c r="D127">
@@ -2945,7 +2945,7 @@
         <v>31.949000000000002</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>126</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>32.048999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>127</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>32.018999999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>128</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>31.971</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>129</v>
       </c>
@@ -3021,15 +3021,15 @@
       <c r="E131">
         <v>32.173000000000002</v>
       </c>
-      <c r="F131" s="2">
+      <c r="F131" s="1">
         <v>32.125</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>130</v>
       </c>
-      <c r="B132" s="2">
+      <c r="B132" s="1">
         <v>32.506</v>
       </c>
       <c r="C132">
@@ -3045,11 +3045,11 @@
         <v>32.015999999999998</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>131</v>
       </c>
-      <c r="B133" s="2">
+      <c r="B133" s="1">
         <v>32.423000000000002</v>
       </c>
       <c r="C133">
@@ -3065,7 +3065,7 @@
         <v>32.109000000000002</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>132</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>32.057000000000002</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>133</v>
       </c>
@@ -3098,21 +3098,21 @@
       <c r="D135">
         <v>32.162999999999997</v>
       </c>
-      <c r="E135" s="2">
+      <c r="E135" s="1">
         <v>32.179000000000002</v>
       </c>
       <c r="F135">
         <v>32.017000000000003</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>134</v>
       </c>
-      <c r="B136" s="2">
+      <c r="B136" s="1">
         <v>32.548000000000002</v>
       </c>
-      <c r="C136" s="2">
+      <c r="C136" s="1">
         <v>32.149000000000001</v>
       </c>
       <c r="D136">
@@ -3125,17 +3125,17 @@
         <v>32.075000000000003</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>135</v>
       </c>
-      <c r="B137" s="2">
+      <c r="B137" s="1">
         <v>32.564999999999998</v>
       </c>
       <c r="C137">
         <v>32.146000000000001</v>
       </c>
-      <c r="D137" s="2">
+      <c r="D137" s="1">
         <v>32.177</v>
       </c>
       <c r="E137">
@@ -3145,11 +3145,11 @@
         <v>32.006</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>136</v>
       </c>
-      <c r="B138" s="2">
+      <c r="B138" s="1">
         <v>32.566000000000003</v>
       </c>
       <c r="C138">
@@ -3165,11 +3165,11 @@
         <v>32.057000000000002</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>137</v>
       </c>
-      <c r="B139" s="2">
+      <c r="B139" s="1">
         <v>32.554000000000002</v>
       </c>
       <c r="C139">
@@ -3185,7 +3185,7 @@
         <v>32.048000000000002</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>138</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>32.075000000000003</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>139</v>
       </c>
@@ -3218,14 +3218,14 @@
       <c r="D141">
         <v>32.155000000000001</v>
       </c>
-      <c r="E141" s="2">
+      <c r="E141" s="1">
         <v>32.183999999999997</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="1">
         <v>32.133000000000003</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>140</v>
       </c>
@@ -3235,7 +3235,7 @@
       <c r="C142">
         <v>32.103000000000002</v>
       </c>
-      <c r="D142" s="2">
+      <c r="D142" s="1">
         <v>32.179000000000002</v>
       </c>
       <c r="E142">
@@ -3245,27 +3245,27 @@
         <v>32.106000000000002</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>141</v>
       </c>
       <c r="B143">
         <v>32.493000000000002</v>
       </c>
-      <c r="C143" s="2">
+      <c r="C143" s="1">
         <v>32.167999999999999</v>
       </c>
-      <c r="D143" s="2">
+      <c r="D143" s="1">
         <v>32.188000000000002</v>
       </c>
-      <c r="E143" s="2">
+      <c r="E143" s="1">
         <v>32.185000000000002</v>
       </c>
       <c r="F143">
         <v>32.128999999999998</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>142</v>
       </c>
@@ -3278,14 +3278,14 @@
       <c r="D144">
         <v>32.164999999999999</v>
       </c>
-      <c r="E144" s="2">
+      <c r="E144" s="1">
         <v>32.198999999999998</v>
       </c>
       <c r="F144">
         <v>32.118000000000002</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>143</v>
       </c>
@@ -3305,14 +3305,14 @@
         <v>32.055999999999997</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>144</v>
       </c>
       <c r="B146">
         <v>32.366999999999997</v>
       </c>
-      <c r="C146" s="2">
+      <c r="C146" s="1">
         <v>32.191000000000003</v>
       </c>
       <c r="D146">
@@ -3325,7 +3325,7 @@
         <v>32.131</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>145</v>
       </c>
@@ -3345,7 +3345,7 @@
         <v>32.128999999999998</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>146</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>32.012</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>147</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>32.104999999999997</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>148</v>
       </c>
@@ -3401,11 +3401,11 @@
       <c r="E150">
         <v>32.142000000000003</v>
       </c>
-      <c r="F150" s="2">
+      <c r="F150" s="1">
         <v>32.133000000000003</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>149</v>
       </c>
@@ -3418,14 +3418,14 @@
       <c r="D151">
         <v>32.173000000000002</v>
       </c>
-      <c r="E151" s="2">
+      <c r="E151" s="1">
         <v>32.213000000000001</v>
       </c>
       <c r="F151">
         <v>32.125999999999998</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>150</v>
       </c>
@@ -3435,21 +3435,21 @@
       <c r="C152">
         <v>32.137</v>
       </c>
-      <c r="D152" s="2">
+      <c r="D152" s="1">
         <v>32.200000000000003</v>
       </c>
       <c r="E152">
         <v>32.198</v>
       </c>
-      <c r="F152" s="2">
+      <c r="F152" s="1">
         <v>32.143999999999998</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>151</v>
       </c>
-      <c r="B153" s="2">
+      <c r="B153" s="1">
         <v>32.545000000000002</v>
       </c>
       <c r="C153">
@@ -3465,7 +3465,7 @@
         <v>32.14</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>152</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>32.087000000000003</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>153</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>32.084000000000003</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>154</v>
       </c>
@@ -3521,15 +3521,15 @@
       <c r="E156">
         <v>32.18</v>
       </c>
-      <c r="F156" s="2">
+      <c r="F156" s="1">
         <v>32.149000000000001</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>155</v>
       </c>
-      <c r="B157" s="2">
+      <c r="B157" s="1">
         <v>32.575000000000003</v>
       </c>
       <c r="C157">
@@ -3541,18 +3541,18 @@
       <c r="E157">
         <v>32.203000000000003</v>
       </c>
-      <c r="F157" s="2">
+      <c r="F157" s="1">
         <v>32.154000000000003</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>156</v>
       </c>
       <c r="B158">
         <v>32.585999999999999</v>
       </c>
-      <c r="C158" s="2">
+      <c r="C158" s="1">
         <v>32.198999999999998</v>
       </c>
       <c r="D158">
@@ -3565,11 +3565,11 @@
         <v>32.146999999999998</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>157</v>
       </c>
-      <c r="B159" s="2">
+      <c r="B159" s="1">
         <v>32.582000000000001</v>
       </c>
       <c r="C159">
@@ -3585,47 +3585,47 @@
         <v>32.125999999999998</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>158</v>
       </c>
       <c r="B160">
         <v>32.594000000000001</v>
       </c>
-      <c r="C160" s="2">
+      <c r="C160" s="1">
         <v>32.206000000000003</v>
       </c>
       <c r="D160">
         <v>32.164999999999999</v>
       </c>
-      <c r="E160" s="2">
+      <c r="E160" s="1">
         <v>32.216999999999999</v>
       </c>
-      <c r="F160" s="2">
+      <c r="F160" s="1">
         <v>32.162999999999997</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>159</v>
       </c>
-      <c r="B161" s="2">
+      <c r="B161" s="1">
         <v>32.581000000000003</v>
       </c>
       <c r="C161">
         <v>32.197000000000003</v>
       </c>
-      <c r="D161" s="2">
+      <c r="D161" s="1">
         <v>32.203000000000003</v>
       </c>
-      <c r="E161" s="2">
+      <c r="E161" s="1">
         <v>32.219000000000001</v>
       </c>
       <c r="F161">
         <v>32.088999999999999</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>160</v>
       </c>
@@ -3635,7 +3635,7 @@
       <c r="C162">
         <v>32.158000000000001</v>
       </c>
-      <c r="D162" s="2">
+      <c r="D162" s="1">
         <v>32.203000000000003</v>
       </c>
       <c r="E162">
@@ -3645,7 +3645,7 @@
         <v>32.152999999999999</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>161</v>
       </c>
@@ -3655,7 +3655,7 @@
       <c r="C163">
         <v>32.146000000000001</v>
       </c>
-      <c r="D163" s="2">
+      <c r="D163" s="1">
         <v>32.225999999999999</v>
       </c>
       <c r="E163">
@@ -3665,7 +3665,7 @@
         <v>32.097000000000001</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>162</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>32.143000000000001</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>163</v>
       </c>
@@ -3701,11 +3701,11 @@
       <c r="E165">
         <v>32.200000000000003</v>
       </c>
-      <c r="F165" s="2">
+      <c r="F165" s="1">
         <v>32.167000000000002</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>164</v>
       </c>
@@ -3718,14 +3718,14 @@
       <c r="D166">
         <v>32.195</v>
       </c>
-      <c r="E166" s="2">
+      <c r="E166" s="1">
         <v>32.220999999999997</v>
       </c>
       <c r="F166">
         <v>32.152999999999999</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>165</v>
       </c>
@@ -3738,14 +3738,14 @@
       <c r="D167">
         <v>32.22</v>
       </c>
-      <c r="E167" s="2">
+      <c r="E167" s="1">
         <v>32.226999999999997</v>
       </c>
       <c r="F167">
         <v>32.152000000000001</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>166</v>
       </c>
@@ -3758,14 +3758,14 @@
       <c r="D168">
         <v>32.222000000000001</v>
       </c>
-      <c r="E168" s="2">
+      <c r="E168" s="1">
         <v>32.256</v>
       </c>
       <c r="F168">
         <v>32.143999999999998</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>167</v>
       </c>
@@ -3785,11 +3785,11 @@
         <v>32.152999999999999</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>168</v>
       </c>
-      <c r="B170" s="2">
+      <c r="B170" s="1">
         <v>32.561999999999998</v>
       </c>
       <c r="C170">
@@ -3805,14 +3805,14 @@
         <v>32.159999999999997</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>169</v>
       </c>
       <c r="B171">
         <v>32.601999999999997</v>
       </c>
-      <c r="C171" s="2">
+      <c r="C171" s="1">
         <v>32.210999999999999</v>
       </c>
       <c r="D171">
@@ -3821,11 +3821,11 @@
       <c r="E171">
         <v>32.194000000000003</v>
       </c>
-      <c r="F171" s="2">
+      <c r="F171" s="1">
         <v>32.195</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>170</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>32.131</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>171</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>32.154000000000003</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>172</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>32.192999999999998</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>173</v>
       </c>
@@ -3905,14 +3905,14 @@
         <v>32.182000000000002</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>174</v>
       </c>
       <c r="B176">
         <v>32.631</v>
       </c>
-      <c r="C176" s="2">
+      <c r="C176" s="1">
         <v>32.216000000000001</v>
       </c>
       <c r="D176">
@@ -3925,11 +3925,11 @@
         <v>32.183999999999997</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>175</v>
       </c>
-      <c r="B177" s="2">
+      <c r="B177" s="1">
         <v>32.598999999999997</v>
       </c>
       <c r="C177">
@@ -3945,7 +3945,7 @@
         <v>32.191000000000003</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>176</v>
       </c>
@@ -3965,7 +3965,7 @@
         <v>32.127000000000002</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>177</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>32.161000000000001</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>178</v>
       </c>
@@ -4005,7 +4005,7 @@
         <v>32.180999999999997</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>179</v>
       </c>
@@ -4015,17 +4015,17 @@
       <c r="C181">
         <v>32.158999999999999</v>
       </c>
-      <c r="D181" s="2">
+      <c r="D181" s="1">
         <v>32.231000000000002</v>
       </c>
-      <c r="E181" s="2">
+      <c r="E181" s="1">
         <v>32.256999999999998</v>
       </c>
       <c r="F181">
         <v>32.149000000000001</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>180</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>32.130000000000003</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>181</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>32.134999999999998</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>182</v>
       </c>
@@ -4075,7 +4075,7 @@
       <c r="C184">
         <v>32.21</v>
       </c>
-      <c r="D184" s="2">
+      <c r="D184" s="1">
         <v>32.232999999999997</v>
       </c>
       <c r="E184">
@@ -4085,14 +4085,14 @@
         <v>32.140999999999998</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>183</v>
       </c>
       <c r="B185">
         <v>32.603999999999999</v>
       </c>
-      <c r="C185" s="2">
+      <c r="C185" s="1">
         <v>32.216000000000001</v>
       </c>
       <c r="D185">
@@ -4105,7 +4105,7 @@
         <v>32.183</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>184</v>
       </c>
@@ -4121,15 +4121,15 @@
       <c r="E186">
         <v>32.21</v>
       </c>
-      <c r="F186" s="2">
+      <c r="F186" s="1">
         <v>32.197000000000003</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>185</v>
       </c>
-      <c r="B187" s="2">
+      <c r="B187" s="1">
         <v>32.639000000000003</v>
       </c>
       <c r="C187">
@@ -4145,11 +4145,11 @@
         <v>32.17</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>186</v>
       </c>
-      <c r="B188" s="2">
+      <c r="B188" s="1">
         <v>32.594999999999999</v>
       </c>
       <c r="C188">
@@ -4165,7 +4165,7 @@
         <v>32.194000000000003</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>187</v>
       </c>
@@ -4175,37 +4175,37 @@
       <c r="C189">
         <v>32.207999999999998</v>
       </c>
-      <c r="D189" s="2">
+      <c r="D189" s="1">
         <v>32.234999999999999</v>
       </c>
       <c r="E189">
         <v>32.247999999999998</v>
       </c>
-      <c r="F189" s="2">
+      <c r="F189" s="1">
         <v>32.198999999999998</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>188</v>
       </c>
       <c r="B190">
         <v>32.582999999999998</v>
       </c>
-      <c r="C190" s="2">
+      <c r="C190" s="1">
         <v>32.220999999999997</v>
       </c>
-      <c r="D190" s="2">
+      <c r="D190" s="1">
         <v>32.237000000000002</v>
       </c>
-      <c r="E190" s="2">
+      <c r="E190" s="1">
         <v>32.270000000000003</v>
       </c>
       <c r="F190">
         <v>32.17</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>189</v>
       </c>
@@ -4225,7 +4225,7 @@
         <v>32.192999999999998</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>190</v>
       </c>
@@ -4245,7 +4245,7 @@
         <v>32.174999999999997</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>191</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>32.183999999999997</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>192</v>
       </c>
@@ -4278,21 +4278,21 @@
       <c r="D194">
         <v>32.228000000000002</v>
       </c>
-      <c r="E194" s="2">
+      <c r="E194" s="1">
         <v>32.274999999999999</v>
       </c>
-      <c r="F194" s="2">
+      <c r="F194" s="1">
         <v>32.218000000000004</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>193</v>
       </c>
       <c r="B195">
         <v>32.607999999999997</v>
       </c>
-      <c r="C195" s="2">
+      <c r="C195" s="1">
         <v>32.241</v>
       </c>
       <c r="D195">
@@ -4305,7 +4305,7 @@
         <v>32.201999999999998</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>194</v>
       </c>
@@ -4321,15 +4321,15 @@
       <c r="E196">
         <v>32.241999999999997</v>
       </c>
-      <c r="F196" s="2">
+      <c r="F196" s="1">
         <v>32.235999999999997</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>195</v>
       </c>
-      <c r="B197" s="2">
+      <c r="B197" s="1">
         <v>32.598999999999997</v>
       </c>
       <c r="C197">
@@ -4345,7 +4345,7 @@
         <v>32.194000000000003</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>196</v>
       </c>
@@ -4355,17 +4355,17 @@
       <c r="C198">
         <v>32.203000000000003</v>
       </c>
-      <c r="D198" s="2">
+      <c r="D198" s="1">
         <v>32.241999999999997</v>
       </c>
-      <c r="E198" s="2">
+      <c r="E198" s="1">
         <v>32.281999999999996</v>
       </c>
       <c r="F198">
         <v>32.207000000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>197</v>
       </c>
@@ -4385,7 +4385,7 @@
         <v>32.204999999999998</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>198</v>
       </c>
@@ -4405,11 +4405,11 @@
         <v>32.198999999999998</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>199</v>
       </c>
-      <c r="B201" s="2">
+      <c r="B201" s="1">
         <v>32.652000000000001</v>
       </c>
       <c r="C201">
@@ -4425,7 +4425,7 @@
         <v>32.116999999999997</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>200</v>
       </c>
@@ -4445,7 +4445,7 @@
         <v>32.213000000000001</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>201</v>
       </c>
@@ -4465,17 +4465,17 @@
         <v>32.216999999999999</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>202</v>
       </c>
-      <c r="B204" s="2">
+      <c r="B204" s="1">
         <v>32.671999999999997</v>
       </c>
       <c r="C204">
         <v>32.225999999999999</v>
       </c>
-      <c r="D204" s="2">
+      <c r="D204" s="1">
         <v>32.243000000000002</v>
       </c>
       <c r="E204">
@@ -4485,17 +4485,17 @@
         <v>32.198</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>203</v>
       </c>
       <c r="B205">
         <v>32.665999999999997</v>
       </c>
-      <c r="C205" s="2">
+      <c r="C205" s="1">
         <v>32.253</v>
       </c>
-      <c r="D205" s="2">
+      <c r="D205" s="1">
         <v>32.244999999999997</v>
       </c>
       <c r="E205">
@@ -4505,7 +4505,7 @@
         <v>32.206000000000003</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>204</v>
       </c>
@@ -4518,14 +4518,14 @@
       <c r="D206">
         <v>32.241</v>
       </c>
-      <c r="E206" s="2">
+      <c r="E206" s="1">
         <v>32.287999999999997</v>
       </c>
       <c r="F206">
         <v>32.207000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>205</v>
       </c>
@@ -4545,7 +4545,7 @@
         <v>32.191000000000003</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>206</v>
       </c>
@@ -4558,14 +4558,14 @@
       <c r="D208">
         <v>32.241</v>
       </c>
-      <c r="E208" s="2">
+      <c r="E208" s="1">
         <v>32.301000000000002</v>
       </c>
       <c r="F208">
         <v>32.21</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>207</v>
       </c>
@@ -4585,11 +4585,11 @@
         <v>32.209000000000003</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>208</v>
       </c>
-      <c r="B210" s="2">
+      <c r="B210" s="1">
         <v>32.677</v>
       </c>
       <c r="C210">
@@ -4605,7 +4605,7 @@
         <v>32.201999999999998</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>209</v>
       </c>
@@ -4625,7 +4625,7 @@
         <v>32.186</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>210</v>
       </c>
@@ -4645,11 +4645,11 @@
         <v>32.204999999999998</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>211</v>
       </c>
-      <c r="B213" s="2">
+      <c r="B213" s="1">
         <v>32.689</v>
       </c>
       <c r="C213">
@@ -4665,7 +4665,7 @@
         <v>32.212000000000003</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>212</v>
       </c>
@@ -4685,7 +4685,7 @@
         <v>32.213999999999999</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>213</v>
       </c>
@@ -4705,14 +4705,14 @@
         <v>32.207000000000001</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>214</v>
       </c>
       <c r="B216">
         <v>32.692</v>
       </c>
-      <c r="C216" s="2">
+      <c r="C216" s="1">
         <v>32.255000000000003</v>
       </c>
       <c r="D216">
@@ -4725,7 +4725,7 @@
         <v>32.209000000000003</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>215</v>
       </c>
@@ -4745,14 +4745,14 @@
         <v>32.218000000000004</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>216</v>
       </c>
       <c r="B218">
         <v>32.715000000000003</v>
       </c>
-      <c r="C218" s="2">
+      <c r="C218" s="1">
         <v>32.265000000000001</v>
       </c>
       <c r="D218">
@@ -4765,14 +4765,14 @@
         <v>32.228000000000002</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>217</v>
       </c>
-      <c r="B219" s="2">
+      <c r="B219" s="1">
         <v>32.661999999999999</v>
       </c>
-      <c r="C219" s="2">
+      <c r="C219" s="1">
         <v>32.265999999999998</v>
       </c>
       <c r="D219">
@@ -4781,18 +4781,18 @@
       <c r="E219">
         <v>32.261000000000003</v>
       </c>
-      <c r="F219" s="2">
+      <c r="F219" s="1">
         <v>32.24</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>218</v>
       </c>
       <c r="B220">
         <v>32.709000000000003</v>
       </c>
-      <c r="C220" s="2">
+      <c r="C220" s="1">
         <v>32.268999999999998</v>
       </c>
       <c r="D220">
@@ -4805,7 +4805,7 @@
         <v>32.188000000000002</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>219</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>32.219000000000001</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>220</v>
       </c>
@@ -4845,7 +4845,7 @@
         <v>32.213999999999999</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>221</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>32.222999999999999</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>222</v>
       </c>
@@ -4885,11 +4885,11 @@
         <v>32.226999999999997</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>223</v>
       </c>
-      <c r="B225" s="2">
+      <c r="B225" s="1">
         <v>32.64</v>
       </c>
       <c r="C225">
@@ -4905,7 +4905,7 @@
         <v>32.231000000000002</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>224</v>
       </c>
@@ -4925,7 +4925,7 @@
         <v>32.222000000000001</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>225</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>32.237000000000002</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>226</v>
       </c>
@@ -4965,14 +4965,14 @@
         <v>32.218000000000004</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>227</v>
       </c>
       <c r="B229">
         <v>32.698</v>
       </c>
-      <c r="C229" s="2">
+      <c r="C229" s="1">
         <v>32.270000000000003</v>
       </c>
       <c r="D229">
@@ -4985,7 +4985,7 @@
         <v>32.22</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>228</v>
       </c>
@@ -4998,14 +4998,14 @@
       <c r="D230">
         <v>32.161999999999999</v>
       </c>
-      <c r="E230" s="2">
+      <c r="E230" s="1">
         <v>32.305</v>
       </c>
       <c r="F230">
         <v>32.234999999999999</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>229</v>
       </c>
@@ -5018,14 +5018,14 @@
       <c r="D231">
         <v>32.158999999999999</v>
       </c>
-      <c r="E231" s="2">
+      <c r="E231" s="1">
         <v>32.311</v>
       </c>
       <c r="F231">
         <v>32.238</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>230</v>
       </c>
@@ -5041,18 +5041,18 @@
       <c r="E232">
         <v>32.279000000000003</v>
       </c>
-      <c r="F232" s="2">
+      <c r="F232" s="1">
         <v>32.241</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>231</v>
       </c>
       <c r="B233">
         <v>32.720999999999997</v>
       </c>
-      <c r="C233" s="2">
+      <c r="C233" s="1">
         <v>32.271999999999998</v>
       </c>
       <c r="D233">
@@ -5065,7 +5065,7 @@
         <v>32.234000000000002</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>232</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>32.22</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>233</v>
       </c>
@@ -5098,14 +5098,14 @@
       <c r="D235">
         <v>32.18</v>
       </c>
-      <c r="E235" s="2">
+      <c r="E235" s="1">
         <v>32.311999999999998</v>
       </c>
-      <c r="F235" s="2">
+      <c r="F235" s="1">
         <v>32.247999999999998</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>234</v>
       </c>
@@ -5125,7 +5125,7 @@
         <v>32.244999999999997</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>235</v>
       </c>
@@ -5141,11 +5141,11 @@
       <c r="E237">
         <v>32.302</v>
       </c>
-      <c r="F237" s="2">
+      <c r="F237" s="1">
         <v>32.25</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>236</v>
       </c>
@@ -5165,7 +5165,7 @@
         <v>32.22</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>237</v>
       </c>
@@ -5185,14 +5185,14 @@
         <v>32.228999999999999</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>238</v>
       </c>
       <c r="B240">
         <v>32.725000000000001</v>
       </c>
-      <c r="C240" s="2">
+      <c r="C240" s="1">
         <v>32.277000000000001</v>
       </c>
       <c r="D240">
@@ -5205,7 +5205,7 @@
         <v>32.238</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>239</v>
       </c>
@@ -5225,14 +5225,14 @@
         <v>32.229999999999997</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>240</v>
       </c>
       <c r="B242">
         <v>32.549999999999997</v>
       </c>
-      <c r="C242" s="2">
+      <c r="C242" s="1">
         <v>32.284999999999997</v>
       </c>
       <c r="D242">
@@ -5241,11 +5241,11 @@
       <c r="E242">
         <v>32.302</v>
       </c>
-      <c r="F242" s="2">
+      <c r="F242" s="1">
         <v>32.25</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>241</v>
       </c>
@@ -5265,7 +5265,7 @@
         <v>32.247999999999998</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>242</v>
       </c>
@@ -5285,7 +5285,7 @@
         <v>32.241</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>243</v>
       </c>
@@ -5305,7 +5305,7 @@
         <v>32.243000000000002</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>244</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>32.241999999999997</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>245</v>
       </c>
@@ -5345,7 +5345,7 @@
         <v>32.235999999999997</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>246</v>
       </c>
@@ -5365,7 +5365,7 @@
         <v>32.241</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>247</v>
       </c>
@@ -5378,14 +5378,14 @@
       <c r="D249">
         <v>32.216999999999999</v>
       </c>
-      <c r="E249" s="2">
+      <c r="E249" s="1">
         <v>32.316000000000003</v>
       </c>
-      <c r="F249" s="2">
+      <c r="F249" s="1">
         <v>32.255000000000003</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>248</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>32.241999999999997</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>249</v>
       </c>
@@ -5425,7 +5425,7 @@
         <v>32.226999999999997</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>250</v>
       </c>
@@ -5445,7 +5445,7 @@
         <v>32.241999999999997</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>251</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>32.244</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>252</v>
       </c>
@@ -5485,14 +5485,14 @@
         <v>32.249000000000002</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>253</v>
       </c>
       <c r="B255">
         <v>32.624000000000002</v>
       </c>
-      <c r="C255" s="2">
+      <c r="C255" s="1">
         <v>32.286000000000001</v>
       </c>
       <c r="D255">
@@ -5505,14 +5505,14 @@
         <v>32.234999999999999</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>254</v>
       </c>
       <c r="B256">
         <v>32.630000000000003</v>
       </c>
-      <c r="C256" s="2">
+      <c r="C256" s="1">
         <v>32.29</v>
       </c>
       <c r="D256">
@@ -5525,7 +5525,7 @@
         <v>32.238</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>255</v>
       </c>
@@ -5545,7 +5545,7 @@
         <v>32.249000000000002</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>256</v>
       </c>
@@ -5565,7 +5565,7 @@
         <v>32.249000000000002</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>257</v>
       </c>
@@ -5578,14 +5578,14 @@
       <c r="D259">
         <v>32.232999999999997</v>
       </c>
-      <c r="E259" s="2">
+      <c r="E259" s="1">
         <v>32.319000000000003</v>
       </c>
       <c r="F259">
         <v>32.252000000000002</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>258</v>
       </c>
@@ -5605,7 +5605,7 @@
         <v>32.237000000000002</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>259</v>
       </c>
@@ -5621,11 +5621,11 @@
       <c r="E261">
         <v>32.299999999999997</v>
       </c>
-      <c r="F261" s="2">
+      <c r="F261" s="1">
         <v>32.256</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>260</v>
       </c>
@@ -5645,7 +5645,7 @@
         <v>32.244</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>261</v>
       </c>
@@ -5661,11 +5661,11 @@
       <c r="E263">
         <v>32.314999999999998</v>
       </c>
-      <c r="F263" s="2">
+      <c r="F263" s="1">
         <v>32.256999999999998</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>262</v>
       </c>
@@ -5685,7 +5685,7 @@
         <v>32.243000000000002</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>263</v>
       </c>
@@ -5695,7 +5695,7 @@
       <c r="C265">
         <v>32.286000000000001</v>
       </c>
-      <c r="D265" s="2">
+      <c r="D265" s="1">
         <v>32.247999999999998</v>
       </c>
       <c r="E265">
@@ -5705,7 +5705,7 @@
         <v>32.247</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>264</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>32.241999999999997</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>265</v>
       </c>
@@ -5738,21 +5738,21 @@
       <c r="D267">
         <v>32.198</v>
       </c>
-      <c r="E267" s="2">
+      <c r="E267" s="1">
         <v>32.320999999999998</v>
       </c>
       <c r="F267">
         <v>32.246000000000002</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>266</v>
       </c>
       <c r="B268">
         <v>32.712000000000003</v>
       </c>
-      <c r="C268" s="2">
+      <c r="C268" s="1">
         <v>32.295999999999999</v>
       </c>
       <c r="D268">
@@ -5765,7 +5765,7 @@
         <v>32.247999999999998</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>267</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>32.252000000000002</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>268</v>
       </c>
@@ -5798,14 +5798,14 @@
       <c r="D270">
         <v>32.244999999999997</v>
       </c>
-      <c r="E270" s="2">
+      <c r="E270" s="1">
         <v>32.320999999999998</v>
       </c>
       <c r="F270">
         <v>32.255000000000003</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>269</v>
       </c>
@@ -5825,7 +5825,7 @@
         <v>32.247</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>270</v>
       </c>
@@ -5845,7 +5845,7 @@
         <v>32.253</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>271</v>
       </c>
@@ -5861,11 +5861,11 @@
       <c r="E273">
         <v>32.313000000000002</v>
       </c>
-      <c r="F273" s="2">
+      <c r="F273" s="1">
         <v>32.26</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>272</v>
       </c>
@@ -5878,14 +5878,14 @@
       <c r="D274">
         <v>32.168999999999997</v>
       </c>
-      <c r="E274" s="3">
+      <c r="E274" s="1">
         <v>32.322000000000003</v>
       </c>
       <c r="F274">
         <v>32.256999999999998</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>273</v>
       </c>
@@ -5895,17 +5895,17 @@
       <c r="C275">
         <v>32.289000000000001</v>
       </c>
-      <c r="D275" s="2">
+      <c r="D275" s="1">
         <v>32.247999999999998</v>
       </c>
       <c r="E275">
         <v>32.314999999999998</v>
       </c>
-      <c r="F275" s="3">
+      <c r="F275" s="1">
         <v>32.265999999999998</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>274</v>
       </c>
@@ -5925,7 +5925,7 @@
         <v>32.26</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>275</v>
       </c>
@@ -5945,7 +5945,7 @@
         <v>32.256</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>276</v>
       </c>
@@ -5965,7 +5965,7 @@
         <v>32.259</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>277</v>
       </c>
@@ -5985,7 +5985,7 @@
         <v>32.258000000000003</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>278</v>
       </c>
@@ -6005,7 +6005,7 @@
         <v>32.253999999999998</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>279</v>
       </c>
@@ -6025,7 +6025,7 @@
         <v>32.261000000000003</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>280</v>
       </c>
@@ -6045,7 +6045,7 @@
         <v>32.26</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>281</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>32.262</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>282</v>
       </c>
@@ -6085,7 +6085,7 @@
         <v>32.256999999999998</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>283</v>
       </c>
@@ -6095,7 +6095,7 @@
       <c r="C285">
         <v>32.290999999999997</v>
       </c>
-      <c r="D285" s="2">
+      <c r="D285" s="1">
         <v>32.250999999999998</v>
       </c>
       <c r="E285">
@@ -6105,7 +6105,7 @@
         <v>32.262</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>284</v>
       </c>
@@ -6125,7 +6125,7 @@
         <v>32.264000000000003</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>285</v>
       </c>
@@ -6135,7 +6135,7 @@
       <c r="C287">
         <v>32.292000000000002</v>
       </c>
-      <c r="D287" s="2">
+      <c r="D287" s="1">
         <v>32.252000000000002</v>
       </c>
       <c r="E287">
@@ -6145,14 +6145,14 @@
         <v>32.259</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>286</v>
       </c>
       <c r="B288">
         <v>32.729999999999997</v>
       </c>
-      <c r="C288" s="3">
+      <c r="C288" s="1">
         <v>32.296999999999997</v>
       </c>
       <c r="D288">
@@ -6165,11 +6165,11 @@
         <v>32.26</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>287</v>
       </c>
-      <c r="B289" s="2">
+      <c r="B289" s="1">
         <v>32.706000000000003</v>
       </c>
       <c r="C289">
@@ -6185,7 +6185,7 @@
         <v>32.264000000000003</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>288</v>
       </c>
@@ -6205,11 +6205,11 @@
         <v>32.26</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>289</v>
       </c>
-      <c r="B291" s="2">
+      <c r="B291" s="1">
         <v>32.725000000000001</v>
       </c>
       <c r="C291">
@@ -6225,7 +6225,7 @@
         <v>32.26</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>290</v>
       </c>
@@ -6245,11 +6245,11 @@
         <v>32.256999999999998</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>291</v>
       </c>
-      <c r="B293" s="2">
+      <c r="B293" s="1">
         <v>32.71</v>
       </c>
       <c r="C293">
@@ -6265,7 +6265,7 @@
         <v>32.262</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>293</v>
       </c>
@@ -6285,7 +6285,7 @@
         <v>32.26</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>294</v>
       </c>
@@ -6305,11 +6305,11 @@
         <v>32.26</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>295</v>
       </c>
-      <c r="B296" s="2">
+      <c r="B296" s="1">
         <v>32.744999999999997</v>
       </c>
       <c r="C296">
@@ -6325,11 +6325,11 @@
         <v>32.261000000000003</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>296</v>
       </c>
-      <c r="B297" s="2">
+      <c r="B297" s="1">
         <v>32.755000000000003</v>
       </c>
       <c r="C297">
@@ -6345,11 +6345,11 @@
         <v>32.26</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>297</v>
       </c>
-      <c r="B298" s="2">
+      <c r="B298" s="1">
         <v>32.767000000000003</v>
       </c>
       <c r="C298">
@@ -6365,7 +6365,7 @@
         <v>32.259</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>298</v>
       </c>
@@ -6375,7 +6375,7 @@
       <c r="C299">
         <v>32.29</v>
       </c>
-      <c r="D299" s="2">
+      <c r="D299" s="1">
         <v>32.256</v>
       </c>
       <c r="E299">
@@ -6385,7 +6385,7 @@
         <v>32.258000000000003</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>299</v>
       </c>
@@ -6405,7 +6405,7 @@
         <v>32.26</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>300</v>
       </c>
@@ -6415,7 +6415,7 @@
       <c r="C301">
         <v>32.292000000000002</v>
       </c>
-      <c r="D301" s="2">
+      <c r="D301" s="1">
         <v>32.256</v>
       </c>
       <c r="E301">
@@ -6425,58 +6425,2205 @@
         <v>32.259</v>
       </c>
     </row>
-    <row r="310" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D310" s="2"/>
-    </row>
-    <row r="312" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B312" s="2"/>
-      <c r="D312" s="2"/>
-    </row>
-    <row r="313" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B313" s="2"/>
-    </row>
-    <row r="316" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B316" s="2"/>
-    </row>
-    <row r="321" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B321" s="2"/>
-    </row>
-    <row r="324" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D324" s="2"/>
-    </row>
-    <row r="326" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D326" s="2"/>
-    </row>
-    <row r="327" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B327" s="2"/>
-    </row>
-    <row r="330" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D330" s="2"/>
-    </row>
-    <row r="335" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D335" s="2"/>
-    </row>
-    <row r="344" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B344" s="2"/>
-    </row>
-    <row r="353" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B353" s="2"/>
-    </row>
-    <row r="376" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D376" s="2"/>
-    </row>
-    <row r="379" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B379" s="2"/>
-    </row>
-    <row r="381" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D381" s="2"/>
-    </row>
-    <row r="390" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B390" s="2"/>
-      <c r="D390" s="3"/>
-    </row>
-    <row r="407" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B407" s="3"/>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A302">
+        <v>301</v>
+      </c>
+      <c r="B302">
+        <v>32.758000000000003</v>
+      </c>
+      <c r="C302">
+        <v>32.24</v>
+      </c>
+      <c r="D302">
+        <v>32.238999999999997</v>
+      </c>
+      <c r="E302">
+        <v>32.308999999999997</v>
+      </c>
+      <c r="F302">
+        <v>32.229999999999997</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A303">
+        <v>302</v>
+      </c>
+      <c r="B303">
+        <v>32.752000000000002</v>
+      </c>
+      <c r="C303">
+        <v>32.255000000000003</v>
+      </c>
+      <c r="D303">
+        <v>32.247</v>
+      </c>
+      <c r="E303">
+        <v>32.284999999999997</v>
+      </c>
+      <c r="F303">
+        <v>32.235999999999997</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A304">
+        <v>303</v>
+      </c>
+      <c r="B304">
+        <v>32.765000000000001</v>
+      </c>
+      <c r="C304">
+        <v>32.247</v>
+      </c>
+      <c r="D304">
+        <v>32.238999999999997</v>
+      </c>
+      <c r="E304">
+        <v>32.247999999999998</v>
+      </c>
+      <c r="F304">
+        <v>32.234000000000002</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A305">
+        <v>304</v>
+      </c>
+      <c r="B305">
+        <v>32.749000000000002</v>
+      </c>
+      <c r="C305">
+        <v>32.274000000000001</v>
+      </c>
+      <c r="D305">
+        <v>32.247</v>
+      </c>
+      <c r="E305">
+        <v>32.289000000000001</v>
+      </c>
+      <c r="F305">
+        <v>32.250999999999998</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A306">
+        <v>305</v>
+      </c>
+      <c r="B306">
+        <v>32.753999999999998</v>
+      </c>
+      <c r="C306">
+        <v>32.283000000000001</v>
+      </c>
+      <c r="D306">
+        <v>32.238999999999997</v>
+      </c>
+      <c r="E306">
+        <v>32.298000000000002</v>
+      </c>
+      <c r="F306">
+        <v>32.235999999999997</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A307">
+        <v>306</v>
+      </c>
+      <c r="B307">
+        <v>32.756</v>
+      </c>
+      <c r="C307">
+        <v>32.262999999999998</v>
+      </c>
+      <c r="D307">
+        <v>32.241</v>
+      </c>
+      <c r="E307">
+        <v>32.283000000000001</v>
+      </c>
+      <c r="F307">
+        <v>32.218000000000004</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A308">
+        <v>307</v>
+      </c>
+      <c r="B308">
+        <v>32.756</v>
+      </c>
+      <c r="C308">
+        <v>32.264000000000003</v>
+      </c>
+      <c r="D308">
+        <v>32.253</v>
+      </c>
+      <c r="E308">
+        <v>32.298999999999999</v>
+      </c>
+      <c r="F308">
+        <v>32.228999999999999</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A309">
+        <v>308</v>
+      </c>
+      <c r="B309">
+        <v>32.759</v>
+      </c>
+      <c r="C309">
+        <v>32.274000000000001</v>
+      </c>
+      <c r="D309">
+        <v>32.255000000000003</v>
+      </c>
+      <c r="E309">
+        <v>32.293999999999997</v>
+      </c>
+      <c r="F309">
+        <v>32.213999999999999</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A310">
+        <v>309</v>
+      </c>
+      <c r="B310">
+        <v>32.76</v>
+      </c>
+      <c r="C310">
+        <v>32.271999999999998</v>
+      </c>
+      <c r="D310" s="1">
+        <v>32.258000000000003</v>
+      </c>
+      <c r="E310">
+        <v>32.289000000000001</v>
+      </c>
+      <c r="F310">
+        <v>32.215000000000003</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A311">
+        <v>310</v>
+      </c>
+      <c r="B311">
+        <v>32.758000000000003</v>
+      </c>
+      <c r="C311">
+        <v>32.26</v>
+      </c>
+      <c r="D311">
+        <v>32.249000000000002</v>
+      </c>
+      <c r="E311">
+        <v>32.313000000000002</v>
+      </c>
+      <c r="F311">
+        <v>32.234000000000002</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A312">
+        <v>311</v>
+      </c>
+      <c r="B312" s="1">
+        <v>32.771999999999998</v>
+      </c>
+      <c r="C312">
+        <v>32.274999999999999</v>
+      </c>
+      <c r="D312" s="1">
+        <v>32.274000000000001</v>
+      </c>
+      <c r="E312">
+        <v>32.317999999999998</v>
+      </c>
+      <c r="F312">
+        <v>32.223999999999997</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A313">
+        <v>312</v>
+      </c>
+      <c r="B313" s="1">
+        <v>32.771999999999998</v>
+      </c>
+      <c r="C313">
+        <v>32.280999999999999</v>
+      </c>
+      <c r="D313">
+        <v>32.262</v>
+      </c>
+      <c r="E313">
+        <v>32.308</v>
+      </c>
+      <c r="F313">
+        <v>32.244999999999997</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A314">
+        <v>313</v>
+      </c>
+      <c r="B314">
+        <v>32.762999999999998</v>
+      </c>
+      <c r="C314">
+        <v>32.265999999999998</v>
+      </c>
+      <c r="D314">
+        <v>32.256</v>
+      </c>
+      <c r="E314">
+        <v>32.313000000000002</v>
+      </c>
+      <c r="F314">
+        <v>32.235999999999997</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A315">
+        <v>314</v>
+      </c>
+      <c r="B315">
+        <v>32.755000000000003</v>
+      </c>
+      <c r="C315">
+        <v>32.286999999999999</v>
+      </c>
+      <c r="D315">
+        <v>32.256</v>
+      </c>
+      <c r="E315">
+        <v>32.277999999999999</v>
+      </c>
+      <c r="F315">
+        <v>32.238</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A316">
+        <v>315</v>
+      </c>
+      <c r="B316" s="1">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C316">
+        <v>32.277000000000001</v>
+      </c>
+      <c r="D316">
+        <v>32.249000000000002</v>
+      </c>
+      <c r="E316">
+        <v>32.287999999999997</v>
+      </c>
+      <c r="F316">
+        <v>32.228000000000002</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A317">
+        <v>316</v>
+      </c>
+      <c r="B317">
+        <v>32.767000000000003</v>
+      </c>
+      <c r="C317">
+        <v>32.268999999999998</v>
+      </c>
+      <c r="D317">
+        <v>32.226999999999997</v>
+      </c>
+      <c r="E317">
+        <v>32.304000000000002</v>
+      </c>
+      <c r="F317">
+        <v>32.238999999999997</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A318">
+        <v>317</v>
+      </c>
+      <c r="B318">
+        <v>32.761000000000003</v>
+      </c>
+      <c r="C318">
+        <v>32.250999999999998</v>
+      </c>
+      <c r="D318">
+        <v>32.268999999999998</v>
+      </c>
+      <c r="E318">
+        <v>32.284999999999997</v>
+      </c>
+      <c r="F318">
+        <v>32.252000000000002</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A319">
+        <v>318</v>
+      </c>
+      <c r="B319">
+        <v>32.753</v>
+      </c>
+      <c r="C319">
+        <v>32.265999999999998</v>
+      </c>
+      <c r="D319">
+        <v>32.262999999999998</v>
+      </c>
+      <c r="E319">
+        <v>32.295999999999999</v>
+      </c>
+      <c r="F319">
+        <v>32.231999999999999</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A320">
+        <v>319</v>
+      </c>
+      <c r="B320">
+        <v>32.771999999999998</v>
+      </c>
+      <c r="C320">
+        <v>32.268999999999998</v>
+      </c>
+      <c r="D320">
+        <v>32.273000000000003</v>
+      </c>
+      <c r="E320">
+        <v>32.301000000000002</v>
+      </c>
+      <c r="F320">
+        <v>32.246000000000002</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A321">
+        <v>320</v>
+      </c>
+      <c r="B321" s="1">
+        <v>32.777999999999999</v>
+      </c>
+      <c r="C321">
+        <v>32.280999999999999</v>
+      </c>
+      <c r="D321">
+        <v>32.273000000000003</v>
+      </c>
+      <c r="E321">
+        <v>32.304000000000002</v>
+      </c>
+      <c r="F321">
+        <v>32.25</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A322">
+        <v>321</v>
+      </c>
+      <c r="B322">
+        <v>32.771000000000001</v>
+      </c>
+      <c r="C322">
+        <v>32.264000000000003</v>
+      </c>
+      <c r="D322">
+        <v>32.26</v>
+      </c>
+      <c r="E322">
+        <v>32.308999999999997</v>
+      </c>
+      <c r="F322">
+        <v>32.234999999999999</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A323">
+        <v>322</v>
+      </c>
+      <c r="B323">
+        <v>32.771000000000001</v>
+      </c>
+      <c r="C323">
+        <v>32.261000000000003</v>
+      </c>
+      <c r="D323">
+        <v>32.26</v>
+      </c>
+      <c r="E323" s="1">
+        <v>32.328000000000003</v>
+      </c>
+      <c r="F323">
+        <v>32.220999999999997</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A324">
+        <v>323</v>
+      </c>
+      <c r="B324">
+        <v>32.768999999999998</v>
+      </c>
+      <c r="C324">
+        <v>32.281999999999996</v>
+      </c>
+      <c r="D324" s="1">
+        <v>32.274999999999999</v>
+      </c>
+      <c r="E324">
+        <v>32.304000000000002</v>
+      </c>
+      <c r="F324">
+        <v>32.238999999999997</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A325">
+        <v>324</v>
+      </c>
+      <c r="B325">
+        <v>32.750999999999998</v>
+      </c>
+      <c r="C325">
+        <v>32.276000000000003</v>
+      </c>
+      <c r="D325">
+        <v>32.265999999999998</v>
+      </c>
+      <c r="E325">
+        <v>32.276000000000003</v>
+      </c>
+      <c r="F325">
+        <v>32.219000000000001</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A326">
+        <v>325</v>
+      </c>
+      <c r="B326">
+        <v>32.72</v>
+      </c>
+      <c r="C326">
+        <v>32.279000000000003</v>
+      </c>
+      <c r="D326" s="1">
+        <v>32.277999999999999</v>
+      </c>
+      <c r="E326">
+        <v>32.323</v>
+      </c>
+      <c r="F326">
+        <v>32.238</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A327">
+        <v>326</v>
+      </c>
+      <c r="B327" s="1">
+        <v>32.783000000000001</v>
+      </c>
+      <c r="C327">
+        <v>32.237000000000002</v>
+      </c>
+      <c r="D327">
+        <v>32.262</v>
+      </c>
+      <c r="E327">
+        <v>32.301000000000002</v>
+      </c>
+      <c r="F327">
+        <v>32.253999999999998</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A328">
+        <v>327</v>
+      </c>
+      <c r="B328">
+        <v>32.780999999999999</v>
+      </c>
+      <c r="C328">
+        <v>32.270000000000003</v>
+      </c>
+      <c r="D328">
+        <v>32.273000000000003</v>
+      </c>
+      <c r="E328">
+        <v>32.302999999999997</v>
+      </c>
+      <c r="F328">
+        <v>32.238999999999997</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A329">
+        <v>328</v>
+      </c>
+      <c r="B329">
+        <v>32.76</v>
+      </c>
+      <c r="C329">
+        <v>32.274999999999999</v>
+      </c>
+      <c r="D329">
+        <v>32.270000000000003</v>
+      </c>
+      <c r="E329">
+        <v>32.305999999999997</v>
+      </c>
+      <c r="F329">
+        <v>32.213000000000001</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A330">
+        <v>329</v>
+      </c>
+      <c r="B330">
+        <v>32.774000000000001</v>
+      </c>
+      <c r="C330" s="2">
+        <v>32.302</v>
+      </c>
+      <c r="D330" s="1">
+        <v>32.286999999999999</v>
+      </c>
+      <c r="E330">
+        <v>32.32</v>
+      </c>
+      <c r="F330">
+        <v>32.258000000000003</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A331">
+        <v>330</v>
+      </c>
+      <c r="B331">
+        <v>32.767000000000003</v>
+      </c>
+      <c r="C331">
+        <v>32.284999999999997</v>
+      </c>
+      <c r="D331">
+        <v>32.271000000000001</v>
+      </c>
+      <c r="E331">
+        <v>32.279000000000003</v>
+      </c>
+      <c r="F331">
+        <v>32.247</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A332">
+        <v>331</v>
+      </c>
+      <c r="B332">
+        <v>32.755000000000003</v>
+      </c>
+      <c r="C332">
+        <v>32.276000000000003</v>
+      </c>
+      <c r="D332">
+        <v>32.276000000000003</v>
+      </c>
+      <c r="E332">
+        <v>32.302999999999997</v>
+      </c>
+      <c r="F332">
+        <v>32.244999999999997</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A333">
+        <v>332</v>
+      </c>
+      <c r="B333">
+        <v>32.768000000000001</v>
+      </c>
+      <c r="C333">
+        <v>32.277999999999999</v>
+      </c>
+      <c r="D333">
+        <v>32.256</v>
+      </c>
+      <c r="E333" s="2">
+        <v>32.337000000000003</v>
+      </c>
+      <c r="F333">
+        <v>32.244</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A334">
+        <v>333</v>
+      </c>
+      <c r="B334">
+        <v>32.765999999999998</v>
+      </c>
+      <c r="C334">
+        <v>32.277999999999999</v>
+      </c>
+      <c r="D334">
+        <v>32.265999999999998</v>
+      </c>
+      <c r="E334">
+        <v>32.302</v>
+      </c>
+      <c r="F334">
+        <v>32.253</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A335">
+        <v>334</v>
+      </c>
+      <c r="B335">
+        <v>32.76</v>
+      </c>
+      <c r="C335">
+        <v>32.289000000000001</v>
+      </c>
+      <c r="D335" s="1">
+        <v>32.292000000000002</v>
+      </c>
+      <c r="E335">
+        <v>32.316000000000003</v>
+      </c>
+      <c r="F335">
+        <v>32.235999999999997</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A336">
+        <v>335</v>
+      </c>
+      <c r="B336">
+        <v>32.762999999999998</v>
+      </c>
+      <c r="C336">
+        <v>32.292999999999999</v>
+      </c>
+      <c r="D336">
+        <v>32.280999999999999</v>
+      </c>
+      <c r="E336">
+        <v>32.316000000000003</v>
+      </c>
+      <c r="F336">
+        <v>32.244999999999997</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A337">
+        <v>336</v>
+      </c>
+      <c r="B337">
+        <v>32.768000000000001</v>
+      </c>
+      <c r="C337">
+        <v>32.293999999999997</v>
+      </c>
+      <c r="D337">
+        <v>32.270000000000003</v>
+      </c>
+      <c r="E337">
+        <v>32.314999999999998</v>
+      </c>
+      <c r="F337">
+        <v>32.252000000000002</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A338">
+        <v>337</v>
+      </c>
+      <c r="B338">
+        <v>32.767000000000003</v>
+      </c>
+      <c r="C338">
+        <v>32.28</v>
+      </c>
+      <c r="D338">
+        <v>32.277999999999999</v>
+      </c>
+      <c r="E338">
+        <v>32.296999999999997</v>
+      </c>
+      <c r="F338">
+        <v>32.246000000000002</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A339">
+        <v>338</v>
+      </c>
+      <c r="B339">
+        <v>32.765000000000001</v>
+      </c>
+      <c r="C339">
+        <v>32.280999999999999</v>
+      </c>
+      <c r="D339">
+        <v>32.29</v>
+      </c>
+      <c r="E339">
+        <v>32.298000000000002</v>
+      </c>
+      <c r="F339">
+        <v>32.262999999999998</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A340">
+        <v>339</v>
+      </c>
+      <c r="B340">
+        <v>32.738999999999997</v>
+      </c>
+      <c r="C340">
+        <v>32.264000000000003</v>
+      </c>
+      <c r="D340">
+        <v>32.284999999999997</v>
+      </c>
+      <c r="E340">
+        <v>32.317999999999998</v>
+      </c>
+      <c r="F340">
+        <v>32.252000000000002</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A341">
+        <v>340</v>
+      </c>
+      <c r="B341">
+        <v>32.773000000000003</v>
+      </c>
+      <c r="C341">
+        <v>32.295000000000002</v>
+      </c>
+      <c r="D341">
+        <v>32.281999999999996</v>
+      </c>
+      <c r="E341">
+        <v>32.308</v>
+      </c>
+      <c r="F341">
+        <v>32.247</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A342">
+        <v>341</v>
+      </c>
+      <c r="B342">
+        <v>32.731999999999999</v>
+      </c>
+      <c r="C342">
+        <v>32.271999999999998</v>
+      </c>
+      <c r="D342">
+        <v>32.274999999999999</v>
+      </c>
+      <c r="E342">
+        <v>32.305999999999997</v>
+      </c>
+      <c r="F342">
+        <v>32.234999999999999</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A343">
+        <v>342</v>
+      </c>
+      <c r="B343">
+        <v>32.752000000000002</v>
+      </c>
+      <c r="C343">
+        <v>32.298000000000002</v>
+      </c>
+      <c r="D343">
+        <v>32.290999999999997</v>
+      </c>
+      <c r="E343">
+        <v>32.323</v>
+      </c>
+      <c r="F343">
+        <v>32.26</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A344">
+        <v>343</v>
+      </c>
+      <c r="B344" s="1">
+        <v>32.786999999999999</v>
+      </c>
+      <c r="C344">
+        <v>32.28</v>
+      </c>
+      <c r="D344">
+        <v>32.289000000000001</v>
+      </c>
+      <c r="E344">
+        <v>32.313000000000002</v>
+      </c>
+      <c r="F344">
+        <v>32.256</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A345">
+        <v>344</v>
+      </c>
+      <c r="B345">
+        <v>32.758000000000003</v>
+      </c>
+      <c r="C345">
+        <v>32.28</v>
+      </c>
+      <c r="D345">
+        <v>32.276000000000003</v>
+      </c>
+      <c r="E345">
+        <v>32.298000000000002</v>
+      </c>
+      <c r="F345" s="1">
+        <v>32.268999999999998</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A346">
+        <v>345</v>
+      </c>
+      <c r="B346">
+        <v>32.777999999999999</v>
+      </c>
+      <c r="C346">
+        <v>32.287999999999997</v>
+      </c>
+      <c r="D346">
+        <v>32.271999999999998</v>
+      </c>
+      <c r="E346">
+        <v>32.304000000000002</v>
+      </c>
+      <c r="F346">
+        <v>32.243000000000002</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A347">
+        <v>346</v>
+      </c>
+      <c r="B347">
+        <v>32.768000000000001</v>
+      </c>
+      <c r="C347">
+        <v>32.287999999999997</v>
+      </c>
+      <c r="D347">
+        <v>32.270000000000003</v>
+      </c>
+      <c r="E347">
+        <v>32.317999999999998</v>
+      </c>
+      <c r="F347">
+        <v>32.261000000000003</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A348">
+        <v>347</v>
+      </c>
+      <c r="B348">
+        <v>32.764000000000003</v>
+      </c>
+      <c r="C348">
+        <v>32.292000000000002</v>
+      </c>
+      <c r="D348">
+        <v>32.277000000000001</v>
+      </c>
+      <c r="E348">
+        <v>32.322000000000003</v>
+      </c>
+      <c r="F348">
+        <v>32.249000000000002</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A349">
+        <v>348</v>
+      </c>
+      <c r="B349">
+        <v>32.756999999999998</v>
+      </c>
+      <c r="C349">
+        <v>32.292000000000002</v>
+      </c>
+      <c r="D349">
+        <v>32.277000000000001</v>
+      </c>
+      <c r="E349">
+        <v>32.290999999999997</v>
+      </c>
+      <c r="F349">
+        <v>32.247</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A350">
+        <v>349</v>
+      </c>
+      <c r="B350">
+        <v>32.762</v>
+      </c>
+      <c r="C350">
+        <v>32.287999999999997</v>
+      </c>
+      <c r="D350">
+        <v>32.277999999999999</v>
+      </c>
+      <c r="E350">
+        <v>32.298000000000002</v>
+      </c>
+      <c r="F350" s="1">
+        <v>32.273000000000003</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A351">
+        <v>350</v>
+      </c>
+      <c r="B351">
+        <v>32.781999999999996</v>
+      </c>
+      <c r="C351">
+        <v>32.293999999999997</v>
+      </c>
+      <c r="D351">
+        <v>32.277999999999999</v>
+      </c>
+      <c r="E351">
+        <v>32.302</v>
+      </c>
+      <c r="F351">
+        <v>32.243000000000002</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A352">
+        <v>351</v>
+      </c>
+      <c r="B352">
+        <v>32.78</v>
+      </c>
+      <c r="C352">
+        <v>32.292000000000002</v>
+      </c>
+      <c r="D352">
+        <v>32.28</v>
+      </c>
+      <c r="E352">
+        <v>32.311999999999998</v>
+      </c>
+      <c r="F352">
+        <v>32.258000000000003</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A353">
+        <v>352</v>
+      </c>
+      <c r="B353" s="1">
+        <v>32.792999999999999</v>
+      </c>
+      <c r="C353">
+        <v>32.276000000000003</v>
+      </c>
+      <c r="D353">
+        <v>32.277000000000001</v>
+      </c>
+      <c r="E353">
+        <v>32.305999999999997</v>
+      </c>
+      <c r="F353">
+        <v>32.265999999999998</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A354">
+        <v>353</v>
+      </c>
+      <c r="B354">
+        <v>32.784999999999997</v>
+      </c>
+      <c r="C354">
+        <v>32.264000000000003</v>
+      </c>
+      <c r="D354">
+        <v>32.277000000000001</v>
+      </c>
+      <c r="E354">
+        <v>32.298999999999999</v>
+      </c>
+      <c r="F354">
+        <v>32.26</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A355">
+        <v>354</v>
+      </c>
+      <c r="B355">
+        <v>32.768999999999998</v>
+      </c>
+      <c r="C355">
+        <v>32.280999999999999</v>
+      </c>
+      <c r="D355">
+        <v>32.286999999999999</v>
+      </c>
+      <c r="E355">
+        <v>32.31</v>
+      </c>
+      <c r="F355">
+        <v>32.253999999999998</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A356">
+        <v>355</v>
+      </c>
+      <c r="B356">
+        <v>32.774000000000001</v>
+      </c>
+      <c r="C356">
+        <v>32.289000000000001</v>
+      </c>
+      <c r="D356">
+        <v>32.28</v>
+      </c>
+      <c r="E356">
+        <v>32.308999999999997</v>
+      </c>
+      <c r="F356">
+        <v>32.256</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A357">
+        <v>356</v>
+      </c>
+      <c r="B357">
+        <v>32.771999999999998</v>
+      </c>
+      <c r="C357">
+        <v>32.295999999999999</v>
+      </c>
+      <c r="D357">
+        <v>32.284999999999997</v>
+      </c>
+      <c r="E357">
+        <v>32.313000000000002</v>
+      </c>
+      <c r="F357">
+        <v>32.258000000000003</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A358">
+        <v>357</v>
+      </c>
+      <c r="B358">
+        <v>32.776000000000003</v>
+      </c>
+      <c r="C358">
+        <v>32.293999999999997</v>
+      </c>
+      <c r="D358">
+        <v>32.283000000000001</v>
+      </c>
+      <c r="E358">
+        <v>32.311999999999998</v>
+      </c>
+      <c r="F358">
+        <v>32.262</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A359">
+        <v>358</v>
+      </c>
+      <c r="B359">
+        <v>32.768999999999998</v>
+      </c>
+      <c r="C359">
+        <v>32.295000000000002</v>
+      </c>
+      <c r="D359">
+        <v>32.277000000000001</v>
+      </c>
+      <c r="E359">
+        <v>32.316000000000003</v>
+      </c>
+      <c r="F359">
+        <v>32.262</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A360">
+        <v>359</v>
+      </c>
+      <c r="B360">
+        <v>32.786999999999999</v>
+      </c>
+      <c r="C360">
+        <v>32.292999999999999</v>
+      </c>
+      <c r="D360">
+        <v>32.29</v>
+      </c>
+      <c r="E360">
+        <v>32.313000000000002</v>
+      </c>
+      <c r="F360">
+        <v>32.253</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A361">
+        <v>360</v>
+      </c>
+      <c r="B361">
+        <v>32.79</v>
+      </c>
+      <c r="C361">
+        <v>32.289000000000001</v>
+      </c>
+      <c r="D361">
+        <v>32.279000000000003</v>
+      </c>
+      <c r="E361">
+        <v>32.317</v>
+      </c>
+      <c r="F361">
+        <v>32.262999999999998</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A362">
+        <v>361</v>
+      </c>
+      <c r="B362">
+        <v>32.765999999999998</v>
+      </c>
+      <c r="C362">
+        <v>32.293999999999997</v>
+      </c>
+      <c r="D362">
+        <v>32.292000000000002</v>
+      </c>
+      <c r="E362">
+        <v>32.317999999999998</v>
+      </c>
+      <c r="F362">
+        <v>32.25</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A363">
+        <v>362</v>
+      </c>
+      <c r="B363">
+        <v>32.777999999999999</v>
+      </c>
+      <c r="C363">
+        <v>32.295000000000002</v>
+      </c>
+      <c r="D363">
+        <v>32.289000000000001</v>
+      </c>
+      <c r="E363">
+        <v>32.314999999999998</v>
+      </c>
+      <c r="F363">
+        <v>32.262</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A364">
+        <v>363</v>
+      </c>
+      <c r="B364">
+        <v>32.783000000000001</v>
+      </c>
+      <c r="C364">
+        <v>32.29</v>
+      </c>
+      <c r="D364">
+        <v>32.29</v>
+      </c>
+      <c r="E364">
+        <v>32.316000000000003</v>
+      </c>
+      <c r="F364">
+        <v>32.262999999999998</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A365">
+        <v>364</v>
+      </c>
+      <c r="B365">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C365">
+        <v>32.290999999999997</v>
+      </c>
+      <c r="D365">
+        <v>32.289000000000001</v>
+      </c>
+      <c r="E365">
+        <v>32.314</v>
+      </c>
+      <c r="F365">
+        <v>32.262999999999998</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A366">
+        <v>365</v>
+      </c>
+      <c r="B366">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C366">
+        <v>32.287999999999997</v>
+      </c>
+      <c r="D366">
+        <v>32.287999999999997</v>
+      </c>
+      <c r="E366">
+        <v>32.316000000000003</v>
+      </c>
+      <c r="F366">
+        <v>32.26</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A367">
+        <v>366</v>
+      </c>
+      <c r="B367">
+        <v>32.784999999999997</v>
+      </c>
+      <c r="C367">
+        <v>32.29</v>
+      </c>
+      <c r="D367">
+        <v>32.287999999999997</v>
+      </c>
+      <c r="E367">
+        <v>32.304000000000002</v>
+      </c>
+      <c r="F367" s="2">
+        <v>32.274999999999999</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A368">
+        <v>367</v>
+      </c>
+      <c r="B368">
+        <v>32.774999999999999</v>
+      </c>
+      <c r="C368">
+        <v>32.292000000000002</v>
+      </c>
+      <c r="D368">
+        <v>32.289000000000001</v>
+      </c>
+      <c r="E368">
+        <v>32.316000000000003</v>
+      </c>
+      <c r="F368">
+        <v>32.268999999999998</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A369">
+        <v>368</v>
+      </c>
+      <c r="B369">
+        <v>32.781999999999996</v>
+      </c>
+      <c r="C369">
+        <v>32.290999999999997</v>
+      </c>
+      <c r="D369">
+        <v>32.284999999999997</v>
+      </c>
+      <c r="E369">
+        <v>32.317</v>
+      </c>
+      <c r="F369">
+        <v>32.268000000000001</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A370">
+        <v>369</v>
+      </c>
+      <c r="B370">
+        <v>32.784999999999997</v>
+      </c>
+      <c r="C370">
+        <v>32.281999999999996</v>
+      </c>
+      <c r="D370">
+        <v>32.286000000000001</v>
+      </c>
+      <c r="E370">
+        <v>32.319000000000003</v>
+      </c>
+      <c r="F370">
+        <v>32.265999999999998</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A371">
+        <v>370</v>
+      </c>
+      <c r="B371">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C371">
+        <v>32.286999999999999</v>
+      </c>
+      <c r="D371">
+        <v>32.281999999999996</v>
+      </c>
+      <c r="E371">
+        <v>32.314999999999998</v>
+      </c>
+      <c r="F371">
+        <v>32.264000000000003</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A372">
+        <v>371</v>
+      </c>
+      <c r="B372">
+        <v>32.78</v>
+      </c>
+      <c r="C372">
+        <v>32.279000000000003</v>
+      </c>
+      <c r="D372">
+        <v>32.281999999999996</v>
+      </c>
+      <c r="E372">
+        <v>32.311</v>
+      </c>
+      <c r="F372">
+        <v>32.256999999999998</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A373">
+        <v>372</v>
+      </c>
+      <c r="B373">
+        <v>32.784999999999997</v>
+      </c>
+      <c r="C373">
+        <v>32.283000000000001</v>
+      </c>
+      <c r="D373">
+        <v>32.283000000000001</v>
+      </c>
+      <c r="E373">
+        <v>32.320999999999998</v>
+      </c>
+      <c r="F373">
+        <v>32.255000000000003</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A374">
+        <v>373</v>
+      </c>
+      <c r="B374">
+        <v>32.786000000000001</v>
+      </c>
+      <c r="C374">
+        <v>32.286999999999999</v>
+      </c>
+      <c r="D374">
+        <v>32.28</v>
+      </c>
+      <c r="E374">
+        <v>32.323</v>
+      </c>
+      <c r="F374">
+        <v>32.261000000000003</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A375">
+        <v>374</v>
+      </c>
+      <c r="B375">
+        <v>32.792000000000002</v>
+      </c>
+      <c r="C375">
+        <v>32.292999999999999</v>
+      </c>
+      <c r="D375">
+        <v>32.286999999999999</v>
+      </c>
+      <c r="E375">
+        <v>32.320999999999998</v>
+      </c>
+      <c r="F375">
+        <v>32.262999999999998</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A376">
+        <v>375</v>
+      </c>
+      <c r="B376">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C376">
+        <v>32.292999999999999</v>
+      </c>
+      <c r="D376" s="1">
+        <v>32.293999999999997</v>
+      </c>
+      <c r="E376">
+        <v>32.32</v>
+      </c>
+      <c r="F376">
+        <v>32.265999999999998</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A377">
+        <v>376</v>
+      </c>
+      <c r="B377">
+        <v>32.779000000000003</v>
+      </c>
+      <c r="C377">
+        <v>32.290999999999997</v>
+      </c>
+      <c r="D377">
+        <v>32.292999999999999</v>
+      </c>
+      <c r="E377">
+        <v>32.320999999999998</v>
+      </c>
+      <c r="F377">
+        <v>32.255000000000003</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A378">
+        <v>377</v>
+      </c>
+      <c r="B378">
+        <v>32.78</v>
+      </c>
+      <c r="C378">
+        <v>32.284999999999997</v>
+      </c>
+      <c r="D378">
+        <v>32.289000000000001</v>
+      </c>
+      <c r="E378">
+        <v>32.331000000000003</v>
+      </c>
+      <c r="F378">
+        <v>32.26</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A379">
+        <v>378</v>
+      </c>
+      <c r="B379" s="1">
+        <v>32.793999999999997</v>
+      </c>
+      <c r="C379">
+        <v>32.289000000000001</v>
+      </c>
+      <c r="D379">
+        <v>32.292000000000002</v>
+      </c>
+      <c r="E379">
+        <v>32.326000000000001</v>
+      </c>
+      <c r="F379">
+        <v>32.26</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A380">
+        <v>379</v>
+      </c>
+      <c r="B380">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C380">
+        <v>32.292999999999999</v>
+      </c>
+      <c r="D380">
+        <v>32.292000000000002</v>
+      </c>
+      <c r="E380">
+        <v>32.317</v>
+      </c>
+      <c r="F380">
+        <v>32.258000000000003</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A381">
+        <v>380</v>
+      </c>
+      <c r="B381">
+        <v>32.780999999999999</v>
+      </c>
+      <c r="C381">
+        <v>32.292999999999999</v>
+      </c>
+      <c r="D381" s="1">
+        <v>32.298000000000002</v>
+      </c>
+      <c r="E381">
+        <v>32.32</v>
+      </c>
+      <c r="F381">
+        <v>32.262999999999998</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A382">
+        <v>381</v>
+      </c>
+      <c r="B382">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C382">
+        <v>32.295000000000002</v>
+      </c>
+      <c r="D382">
+        <v>32.292999999999999</v>
+      </c>
+      <c r="E382">
+        <v>32.323</v>
+      </c>
+      <c r="F382">
+        <v>32.256</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A383">
+        <v>382</v>
+      </c>
+      <c r="B383">
+        <v>32.793999999999997</v>
+      </c>
+      <c r="C383">
+        <v>32.290999999999997</v>
+      </c>
+      <c r="D383">
+        <v>32.293999999999997</v>
+      </c>
+      <c r="E383">
+        <v>32.323</v>
+      </c>
+      <c r="F383">
+        <v>32.264000000000003</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A384">
+        <v>383</v>
+      </c>
+      <c r="B384">
+        <v>32.793999999999997</v>
+      </c>
+      <c r="C384">
+        <v>32.286000000000001</v>
+      </c>
+      <c r="D384">
+        <v>32.293999999999997</v>
+      </c>
+      <c r="E384">
+        <v>32.319000000000003</v>
+      </c>
+      <c r="F384">
+        <v>32.261000000000003</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A385">
+        <v>384</v>
+      </c>
+      <c r="B385">
+        <v>32.792999999999999</v>
+      </c>
+      <c r="C385">
+        <v>32.283999999999999</v>
+      </c>
+      <c r="D385">
+        <v>32.293999999999997</v>
+      </c>
+      <c r="E385">
+        <v>32.326000000000001</v>
+      </c>
+      <c r="F385">
+        <v>32.265999999999998</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A386">
+        <v>385</v>
+      </c>
+      <c r="B386">
+        <v>32.786999999999999</v>
+      </c>
+      <c r="C386">
+        <v>32.286000000000001</v>
+      </c>
+      <c r="D386">
+        <v>32.292999999999999</v>
+      </c>
+      <c r="E386">
+        <v>32.325000000000003</v>
+      </c>
+      <c r="F386">
+        <v>32.262999999999998</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A387">
+        <v>386</v>
+      </c>
+      <c r="B387">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C387">
+        <v>32.289000000000001</v>
+      </c>
+      <c r="D387">
+        <v>32.290999999999997</v>
+      </c>
+      <c r="E387">
+        <v>32.326999999999998</v>
+      </c>
+      <c r="F387">
+        <v>32.267000000000003</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A388">
+        <v>387</v>
+      </c>
+      <c r="B388">
+        <v>32.774000000000001</v>
+      </c>
+      <c r="C388">
+        <v>32.293999999999997</v>
+      </c>
+      <c r="D388">
+        <v>32.292000000000002</v>
+      </c>
+      <c r="E388">
+        <v>32.32</v>
+      </c>
+      <c r="F388">
+        <v>32.270000000000003</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A389">
+        <v>388</v>
+      </c>
+      <c r="B389">
+        <v>32.758000000000003</v>
+      </c>
+      <c r="C389">
+        <v>32.292000000000002</v>
+      </c>
+      <c r="D389">
+        <v>32.29</v>
+      </c>
+      <c r="E389">
+        <v>32.328000000000003</v>
+      </c>
+      <c r="F389">
+        <v>32.259</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A390">
+        <v>389</v>
+      </c>
+      <c r="B390" s="1">
+        <v>32.802999999999997</v>
+      </c>
+      <c r="C390">
+        <v>32.295000000000002</v>
+      </c>
+      <c r="D390" s="2">
+        <v>32.298999999999999</v>
+      </c>
+      <c r="E390">
+        <v>32.326999999999998</v>
+      </c>
+      <c r="F390">
+        <v>32.262</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A391">
+        <v>390</v>
+      </c>
+      <c r="B391">
+        <v>32.787999999999997</v>
+      </c>
+      <c r="C391">
+        <v>32.289000000000001</v>
+      </c>
+      <c r="D391">
+        <v>32.293999999999997</v>
+      </c>
+      <c r="E391">
+        <v>32.322000000000003</v>
+      </c>
+      <c r="F391">
+        <v>32.265000000000001</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A392">
+        <v>391</v>
+      </c>
+      <c r="B392">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C392">
+        <v>32.283000000000001</v>
+      </c>
+      <c r="D392">
+        <v>32.293999999999997</v>
+      </c>
+      <c r="E392">
+        <v>32.325000000000003</v>
+      </c>
+      <c r="F392">
+        <v>32.265000000000001</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A393">
+        <v>392</v>
+      </c>
+      <c r="B393">
+        <v>32.787999999999997</v>
+      </c>
+      <c r="C393">
+        <v>32.289000000000001</v>
+      </c>
+      <c r="D393">
+        <v>32.290999999999997</v>
+      </c>
+      <c r="E393">
+        <v>32.323</v>
+      </c>
+      <c r="F393">
+        <v>32.265999999999998</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A394">
+        <v>393</v>
+      </c>
+      <c r="B394">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C394">
+        <v>32.29</v>
+      </c>
+      <c r="D394">
+        <v>32.292999999999999</v>
+      </c>
+      <c r="E394">
+        <v>32.322000000000003</v>
+      </c>
+      <c r="F394">
+        <v>32.267000000000003</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A395">
+        <v>394</v>
+      </c>
+      <c r="B395">
+        <v>32.768000000000001</v>
+      </c>
+      <c r="C395">
+        <v>32.290999999999997</v>
+      </c>
+      <c r="D395">
+        <v>32.29</v>
+      </c>
+      <c r="E395">
+        <v>32.316000000000003</v>
+      </c>
+      <c r="F395">
+        <v>32.265000000000001</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A396">
+        <v>395</v>
+      </c>
+      <c r="B396">
+        <v>32.78</v>
+      </c>
+      <c r="C396">
+        <v>32.289000000000001</v>
+      </c>
+      <c r="D396">
+        <v>32.29</v>
+      </c>
+      <c r="E396">
+        <v>32.317999999999998</v>
+      </c>
+      <c r="F396">
+        <v>32.267000000000003</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A397">
+        <v>396</v>
+      </c>
+      <c r="B397">
+        <v>32.779000000000003</v>
+      </c>
+      <c r="C397">
+        <v>32.290999999999997</v>
+      </c>
+      <c r="D397">
+        <v>32.293999999999997</v>
+      </c>
+      <c r="E397">
+        <v>32.325000000000003</v>
+      </c>
+      <c r="F397">
+        <v>32.265000000000001</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A398">
+        <v>397</v>
+      </c>
+      <c r="B398">
+        <v>32.781999999999996</v>
+      </c>
+      <c r="C398">
+        <v>32.292999999999999</v>
+      </c>
+      <c r="D398">
+        <v>32.293999999999997</v>
+      </c>
+      <c r="E398">
+        <v>32.323</v>
+      </c>
+      <c r="F398">
+        <v>32.268000000000001</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A399">
+        <v>398</v>
+      </c>
+      <c r="B399">
+        <v>32.78</v>
+      </c>
+      <c r="C399">
+        <v>32.292000000000002</v>
+      </c>
+      <c r="D399">
+        <v>32.290999999999997</v>
+      </c>
+      <c r="E399">
+        <v>32.326999999999998</v>
+      </c>
+      <c r="F399">
+        <v>32.264000000000003</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A400">
+        <v>399</v>
+      </c>
+      <c r="B400">
+        <v>32.789000000000001</v>
+      </c>
+      <c r="C400">
+        <v>32.292999999999999</v>
+      </c>
+      <c r="D400">
+        <v>32.292999999999999</v>
+      </c>
+      <c r="E400">
+        <v>32.322000000000003</v>
+      </c>
+      <c r="F400">
+        <v>32.271000000000001</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A401">
+        <v>400</v>
+      </c>
+      <c r="B401">
+        <v>32.780999999999999</v>
+      </c>
+      <c r="C401">
+        <v>32.292000000000002</v>
+      </c>
+      <c r="D401">
+        <v>32.295000000000002</v>
+      </c>
+      <c r="E401">
+        <v>32.326000000000001</v>
+      </c>
+      <c r="F401">
+        <v>32.274000000000001</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A402">
+        <v>401</v>
+      </c>
+      <c r="B402">
+        <v>32.779000000000003</v>
+      </c>
+      <c r="C402">
+        <v>32.292000000000002</v>
+      </c>
+      <c r="D402">
+        <v>32.295000000000002</v>
+      </c>
+      <c r="E402">
+        <v>32.326000000000001</v>
+      </c>
+      <c r="F402">
+        <v>32.267000000000003</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A403">
+        <v>402</v>
+      </c>
+      <c r="B403">
+        <v>32.768999999999998</v>
+      </c>
+      <c r="C403">
+        <v>32.295000000000002</v>
+      </c>
+      <c r="D403">
+        <v>32.293999999999997</v>
+      </c>
+      <c r="E403">
+        <v>32.322000000000003</v>
+      </c>
+      <c r="F403">
+        <v>32.267000000000003</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A404">
+        <v>403</v>
+      </c>
+      <c r="B404">
+        <v>32.787999999999997</v>
+      </c>
+      <c r="C404">
+        <v>32.292000000000002</v>
+      </c>
+      <c r="D404">
+        <v>32.295999999999999</v>
+      </c>
+      <c r="E404">
+        <v>32.325000000000003</v>
+      </c>
+      <c r="F404">
+        <v>32.268999999999998</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A405">
+        <v>404</v>
+      </c>
+      <c r="B405">
+        <v>32.765999999999998</v>
+      </c>
+      <c r="C405">
+        <v>32.289000000000001</v>
+      </c>
+      <c r="D405">
+        <v>32.292999999999999</v>
+      </c>
+      <c r="E405">
+        <v>32.326999999999998</v>
+      </c>
+      <c r="F405">
+        <v>32.268000000000001</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A406">
+        <v>405</v>
+      </c>
+      <c r="B406">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C406">
+        <v>32.292000000000002</v>
+      </c>
+      <c r="D406">
+        <v>32.292999999999999</v>
+      </c>
+      <c r="E406">
+        <v>32.320999999999998</v>
+      </c>
+      <c r="F406">
+        <v>32.271000000000001</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A407">
+        <v>406</v>
+      </c>
+      <c r="B407" s="2">
+        <v>32.804000000000002</v>
+      </c>
+      <c r="C407">
+        <v>32.290999999999997</v>
+      </c>
+      <c r="D407">
+        <v>32.292999999999999</v>
+      </c>
+      <c r="E407">
+        <v>32.323999999999998</v>
+      </c>
+      <c r="F407">
+        <v>32.268000000000001</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A408">
+        <v>407</v>
+      </c>
+      <c r="B408">
+        <v>32.777000000000001</v>
+      </c>
+      <c r="C408">
+        <v>32.290999999999997</v>
+      </c>
+      <c r="D408">
+        <v>32.292000000000002</v>
+      </c>
+      <c r="E408">
+        <v>32.32</v>
+      </c>
+      <c r="F408">
+        <v>32.268000000000001</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A409">
+        <v>408</v>
+      </c>
+      <c r="B409">
+        <v>32.792000000000002</v>
+      </c>
+      <c r="C409">
+        <v>32.292000000000002</v>
+      </c>
+      <c r="D409">
+        <v>32.295000000000002</v>
+      </c>
+      <c r="E409">
+        <v>32.323</v>
+      </c>
+      <c r="F409">
+        <v>32.270000000000003</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A410">
+        <v>409</v>
+      </c>
+      <c r="B410">
+        <v>32.781999999999996</v>
+      </c>
+      <c r="C410">
+        <v>32.292999999999999</v>
+      </c>
+      <c r="D410">
+        <v>32.293999999999997</v>
+      </c>
+      <c r="E410">
+        <v>32.323</v>
+      </c>
+      <c r="F410">
+        <v>32.268999999999998</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A411">
+        <v>410</v>
+      </c>
+      <c r="B411">
+        <v>32.776000000000003</v>
+      </c>
+      <c r="C411">
+        <v>32.292000000000002</v>
+      </c>
+      <c r="D411">
+        <v>32.293999999999997</v>
+      </c>
+      <c r="E411">
+        <v>32.323</v>
+      </c>
+      <c r="F411">
+        <v>32.271000000000001</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
